--- a/odoo_tracker_results.xlsx
+++ b/odoo_tracker_results.xlsx
@@ -1,13 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facebook Leads" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LinkedIn Jobs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LinkedIn Posts" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +44,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,421 +415,3834 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>post_url</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>author_url</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>post_text</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>job_title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>job_url</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>description</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-04T04:23:25.000Z</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/odoodevelopers/permalink/2515440338896882/</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>Analyst/ Senior Analyst, Pricing Marketing (Bangkok Based, relocation provided)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Agoda</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>كيفية استخدام Price Lists في Odoo لإدارة أسعار المنتجات بطريقة احترافية.
-✅ ما هي Price Lists؟
-✅ إنشاء قائمة أسعار جديدة.
-✅ تحديد أسعار مختلفة حسب العميل أو المجموعة.
-✅ تطبيق خصومات وعروض تلقائية.
-✅ تحديد فترة زمنية لقائمة الأسعار.
-✅ التسعير حسب الكمية.
-✅ أفضل الممارسات لتجنب أخطاء التسعير.
-إذا كنت تعمل على Odoo في المبيعات أو الحسابات أو إدارة الأعمال، فهذا الفيديو سيساعدك على إعداد نظام تسعير مرن واحترافي.</t>
+          <t>Al Rayyan, Al Rayyan, Qatar</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://qa.linkedin.com/jobs/view/analyst-senior-analyst-pricing-marketing-bangkok-based-relocation-provided-at-agoda-4410528564?position=58&amp;pageNum=0&amp;refId=UtMb0d%2FWMrj%2F5tc%2F6X8BlQ%3D%3D&amp;trackingId=dISKpPHwJFXP4BvQtPELJQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>About Agoda
+At Agoda, we bridge the world through travel. Our story began in 2005, when two lifelong friends and entrepreneurs, driven by their passion for travel, launched Agoda to make it easier for everyone to explore the world.
+Today, we are part of Booking Holdings [NASDAQ: BKNG], with a dive...</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-04T10:00:50.000Z</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/108562316441131/permalink/2018508195446524/</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>Analyst/ Senior Analyst, Pricing Marketing (Bangkok Based, relocation provided)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Agoda</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>اهلا بيكم في جروب Odoo ERP ساهم بأسئلتك وفيديوهاتك وعروضك مع تمنياتي بالتوفيق محاسب قانوني عادل طيبي 
-01017518091
-Adham Elmalke,
-Menna Salama,
-Mohamed Ashraf,
-Bashar Kh,
-Mohamed Osama,
-Elsayed Ibrahim,
-Weerut Pan,
-Ahoud S. Youssef,
-Emad Zayan,
-Tzunə,
-الباز أفندي سمسار وقباني,
-ميادة رمضان,
-Ahmed Tamer,
-Ad Support Pro</t>
+          <t>Doha, Qatar</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://qa.linkedin.com/jobs/view/analyst-senior-analyst-pricing-marketing-bangkok-based-relocation-provided-at-agoda-4410541459?position=52&amp;pageNum=0&amp;refId=UtMb0d%2FWMrj%2F5tc%2F6X8BlQ%3D%3D&amp;trackingId=9HWI8dTNMEabI5c1EVngIg%3D%3D</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>About Agoda
+At Agoda, we bridge the world through travel. Our story began in 2005, when two lifelong friends and entrepreneurs, driven by their passion for travel, launched Agoda to make it easier for everyone to explore the world.
+Today, we are part of Booking Holdings [NASDAQ: BKNG], with a dive...</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-03T09:37:29.000Z</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/108562316441131/permalink/2017610682202942/</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>Senior Analyst, App Marketing (Bangkok Based, Relocation Provided)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Agoda</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>اهلا بيكم في جروب Odoo ERP ساهم بأسئلتك وفيديوهاتك وعروضك مع تمنياتي بالتوفيق محاسب قانوني عادل طيبي 
-01017518091
-البداية سر النجاح ,
-Mariem Tawfek,
-Youssef Anous Elseginy,
-Nour Magdi,
-Ahmed Profo,
-Omar Alsayed,
-Adan Garnica Carrillo,
-Nabil Eldeeb,
-SK Technology - Odoo ERP Services</t>
+          <t>Al Rayyan, Al Rayyan, Qatar</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://qa.linkedin.com/jobs/view/senior-analyst-app-marketing-bangkok-based-relocation-provided-at-agoda-4410540367?position=56&amp;pageNum=0&amp;refId=UtMb0d%2FWMrj%2F5tc%2F6X8BlQ%3D%3D&amp;trackingId=%2FJvIYrn9CfLhthFljaE5xQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>About Agoda
+At Agoda, we bridge the world through travel. Our story began in 2005, when two lifelong friends and entrepreneurs, driven by their passion for travel, launched Agoda to make it easier for everyone to explore the world.
+Today, we are part of Booking Holdings [NASDAQ: BKNG], with a dive...</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-03T02:07:30.000Z</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/108562316441131/permalink/2017337728896904/</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>Senior Analyst/ Associate Manager, Marketing Strategy (Bangkok based/ Relocation provided)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Agoda</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>منفذين لاكثر من مشروع بنفس النشاط في مصر و السعوديه و الكويت و عمان
-Odoo gold partner 
-Experience From 2015
-Free Demo 
- Contact Us 01065031118</t>
+          <t>Al Rayyan, Al Rayyan, Qatar</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://qa.linkedin.com/jobs/view/senior-analyst-associate-manager-marketing-strategy-bangkok-based-relocation-provided-at-agoda-4410549207?position=57&amp;pageNum=0&amp;refId=UtMb0d%2FWMrj%2F5tc%2F6X8BlQ%3D%3D&amp;trackingId=f41o1aR0WQWhQ4xw9tY7hg%3D%3D</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>About Agoda
+At Agoda, we bridge the world through travel. Our story began in 2005, when two lifelong friends and entrepreneurs, driven by their passion for travel, launched Agoda to make it easier for everyone to explore the world.
+Today, we are part of Booking Holdings [NASDAQ: BKNG], with a dive...</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-02T21:05:23.000Z</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/108562316441131/permalink/2017172768913400/</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>KFM</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>اهلا بيكم في جروب Odoo ERP ساهم بأسئلتك وفيديوهاتك وعروضك مع تمنياتي بالتوفيق محاسب قانوني عادل طيبي 
-01017518091
-Aydin Karavelioglu,
-Missaoui Alia,
-Myint M M Ko,
-Smart System ,
-Nguyễn Phúc Đỉnh,
-Mahmoud Yousry Helali,
-Okwong Philemon,
-Tarek Mohsen,
-Hasan Okasha,
-Hussein Dm,
-Mohamed Youssef,
-Mustafa Suleiman,
-Mehedi Hasan Bondhon,
-Ahmed Shrief,
-تالية القرآن,
-Mohammad Almowafy,
-Mohamed Hatem El Sayed,
-عصام نادى</t>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://bh.linkedin.com/jobs/view/host-at-kfm-4418728724?position=7&amp;pageNum=0&amp;refId=e870szcZe7SoL3O%2BUMfvHg%3D%3D&amp;trackingId=XjiRxSUmwf%2FBcBz2KhwhYA%3D%3D</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>About Khosh Fkra Media (KFM)
+Khosh Fkra Media (www.khoshfkramedia.com) was founded in 2020 with a vision to transform the digital landscape. Today, we've grown into a 70+ strong team, and our platforms reach over 12 million people across the GCC every month.
+We're best known for our captivating sh...</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-02T09:26:43.000Z</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/108562316441131/permalink/2016344915662852/</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>AI Video Creator</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>The Flex</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>#هـــــــــــام 💪💪
- مجال تحليل البيانات ( 𝐃𝐚𝐭𝐚 𝐚𝐧𝐚𝐥𝐲𝐬𝐢𝐬)
-لو اخدت كل يوم نص ساعه من وقتك تتعلم فيها هتنقل نفسك في حته تانيه خالص بكارير وعلم جديد يضيف لمستقبلك
-مجال تحليل البيانات من أكتر  المجالات المطلوبه لعام 2030 ومستقبله حقيقي مهم جداا وبيتطور كل يوم ومرتباته كويسه جدااااا الرد بنعم لأضافتك</t>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://bh.linkedin.com/jobs/view/ai-video-creator-at-the-flex-4436785103?position=8&amp;pageNum=0&amp;refId=e870szcZe7SoL3O%2BUMfvHg%3D%3D&amp;trackingId=gjYFJ1uqrjicAd14mp5Zsg%3D%3D</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>About The Role
+We're looking for an AI Video Creator to own how Base360 shows up in the world on video. You'll turn our product into launch videos, ads, and social content that stop the scroll and make people feel something. This is a creative, hands-on role for someone who lives at the intersectio...</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-03T20:31:50.000Z</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/odoodevelopers/permalink/2515165228924393/</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>Digital Marketing &amp; Communications Assistant Manager</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Four Seasons</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>هنبدأ  أول برزنتيشن لتعلم الOdoo الرد بنعم لتضاف 
-بالاضافه الي ملفات pdf المجانية</t>
+          <t>Manama, Capital Governorate, Bahrain</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://bh.linkedin.com/jobs/view/digital-marketing-communications-assistant-manager-at-four-seasons-4435836394?position=6&amp;pageNum=0&amp;refId=e870szcZe7SoL3O%2BUMfvHg%3D%3D&amp;trackingId=Whzlz9sG7pS1NliLyEbwcQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>About Four Seasons
+Four Seasons is powered by our people. We are a collective of individuals who crave to become better, to push ourselves to new heights and to treat each other as we wish to be treated in return. Our team members around the world create amazing experiences for our guests, resident...</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-03T14:39:53.000Z</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/odoodevelopers/permalink/2514913042282945/</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>Sales Support Executive</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>VerifiedJobs.ae</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>#تريكات_Odoo_Advanced 😉 
-موضوع النهاردة: أتمتة حساب إجمالي عدد المنتجات في أوامر البيع، الشراء، والمخازن 📊 الخيار الذكي البديل للآلة الحاسبة!
-واحدة من أكتر الحاجات المزعجة للمحاسبين وأمناء المخازن لما يستلموا أو يبيعوا أوردر فيه 20 أو 30 صنف، هي إنهم يضطروا يجمعوا كميات السطور يدوياً عشان يتأكدوا إن إجمالي عدد القطع (Total Items/Qty) مظبوط مع الشحنة الفعلية.
-في تريكة النهاردة، هوريك إزاي بـ Computed Field بسيط وسلس، تخلي أودو يحسب لك إجمالي عدد القطع جوه أمر البيع (Sales Order)، أمر الشراء (Purchase Order)، أو حتى إذن التحويل المخزني (Stock Transfer) تلقائياً ولحظياً!
-✅ الفكرة والحل البرمجي: إضافة حقل مخصص (Custom Field) يعتمد على كود بايثون بسيط (Depends) بيلف على بنود الأوردر (Order Lines) ويجمع كل الكميات المكتوبة عشان يظهر لك الإجمالي في أسفل الصفحة جنب الضرائب والإجمالي المالي.
-✅ النتائج اللي هتشوفها في الفيديو: 
-1️⃣ سرعة الرقابة والجرد: أمين المخزن هيطابق إجمالي القطع في الكرتونة مع الرقم الظاهر على السيستم في ثانية واحدة. 
-2️⃣ تطبيق مرن: الشرح هيغطّي إزاي تطبق التريكة دي في 3 موديولات أساسية (المبيعات، المشتريات، والمخازن). 
-3️⃣ تحديث لحظي: بمجرد تعديل كمية أي صنف في السطور، إجمالي القطع بيتحدث تلقائياً بدون حاجة لحفظ الأوردر أولاً.
-✅ الهدف النهائي: نلغي تماماً احتمالية الخطأ البشري في تجميع الكميات، ونوفر وقت فريق العمل في العمليات اليومية المتكررة. 🎯
-السيستم الشاطر هو اللي بيوفر وقت موظفينه بلمحة عين. 🎯
-شاهد الفيديو والكود المستخدم من هنا: [https://lnkd.in/datCvdjz] 🔗
-hashtag#Odoo_Development hashtag#Python hashtag#Computed_Fields hashtag#Odoo19 hashtag#Inventory_Management hashtag#Sales_Order hashtag#Purchase_Order hashtag#Advanced_Odoo hashtag#Automation hashtag#Egypt hashtag#Ali_Mohamed hashtag#odoo</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/sales-support-executive-at-verifiedjobs-ae-4439058832?position=58&amp;pageNum=0&amp;refId=XmMWvo8aKI%2BTS%2FC4M9t72A%3D%3D&amp;trackingId=1fYConrr5oCfHWo3CDenCw%3D%3D</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Job Description
+Job Purpose: Provide comprehensive support to the trade, corporate and direct customers across all sales channels within UAE Sales with high level of efficiency to deliver results. Collaborate with the field sales force and commercial managers on all sales and marketing activities w...</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-02T09:26:43.000Z</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/108562316441131/permalink/2016128632351147/</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>Real Estate Sales Agent</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Pangea Dubai</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>هنبدأ  أول برزنتيشن لتعلم الOdoo الرد بنعم لتضاف 
-بالاضافه الي ملفات pdf المجانية</t>
+          <t>Dubai, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/real-estate-sales-agent-at-pangea-dubai-4430416080?position=60&amp;pageNum=0&amp;refId=XmMWvo8aKI%2BTS%2FC4M9t72A%3D%3D&amp;trackingId=KvOlYQgkkFxqLO8bwT2Q8g%3D%3D</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Are you ready to take your career to the next level in one of the most exciting real estate markets in the world? We’re looking for dynamic, financially driven, and disciplined professionals from the UK to join our high-performing team here in Dubai.
+What You’ll Do:
+- Build and maintain strong c...</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-02T09:26:43.000Z</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/108562316441131/permalink/2013025452661465/</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>Associate Marketing Specialist</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>McDermott International, Ltd</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>منحة للطلبة والخارجين والجميع
-تدريب الodoo
-تدريب الic3
-تدريب الpmp
-دراسة الماجستير 
-منحة مجانية للتعليم والتأهيل المهني لفرص العمل 
-تم وهبعتلك لينك الانضمام</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/associate-marketing-specialist-at-mcdermott-international-ltd-4437152521?position=57&amp;pageNum=0&amp;refId=XmMWvo8aKI%2BTS%2FC4M9t72A%3D%3D&amp;trackingId=NOSOfyzUeVz7hjjMpbk1dQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Job Description
+Job Overview:
+The Associate Marketing Specialist is responsible for utilizing existing Marketing procedures to solve routine or standard problems. They receive instruction, guidance, and direction from others within the team, and they will leverage their conceptual knowledge of the...</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-03T12:04:03.000Z</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/odoodevelopers/permalink/2514792522294997/</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Aldhafra Resort, Vignette Collection by IHG</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>فرصه لكل المحاسبين 
- تبدأ محاضرات ال Odoo 
-الخميس القادم اول محاضرة مجانية من يريد الانضمام يترك تم</t>
+          <t>Abu Dhabi Emirate, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/marketing-manager-at-aldhafra-resort-vignette-collection-by-ihg-4426947159?position=56&amp;pageNum=0&amp;refId=XmMWvo8aKI%2BTS%2FC4M9t72A%3D%3D&amp;trackingId=0IeRpxbcmeFhQ50Vs9Ruyw%3D%3D</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>About Us
+Aldhafra Resort, a serene desert retreat, is nestled on the edge of the Rub’ al Khali, the world’s largest uninterrupted sand desert, just a short distance from the heart of Abu Dhabi. Blending the natural beauty of the desert with warm hospitality, the resort offers a welcoming escape for...</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-03T06:54:14.000Z</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/odoodevelopers/permalink/2514581058982810/</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>Marketing Manager - Food &amp; Beverage</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Yas Plaza Hotels by Aldar Hospitality</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AI Is Powerful. Experience Makes It Valuable.
-Recently, there has been significant discussion around reports that Ford brought back experienced engineers after realizing that AI and automation alone were not delivering the expected quality outcomes. The lesson here is not that AI failed — the lesson is that AI without experience has limitations.
-This creates an important message for all of us in the technology and business world:
-AI is a tool. A very powerful one.
-It can:
-✅ Increase speed
-✅ Automate repetitive tasks
-✅ Process large amounts of information
-✅ Improve productivity
-But practical judgment, business understanding, real-world problem-solving, and years of hands-on experience cannot simply be replaced by algorithms.
-The Ford example highlights a reality many organizations are beginning to understand: machines can assist, but experienced people provide context, direction, and decision-making.
-As ERP professionals, we see the same reality across industries. Technology alone is not enough. Understanding business processes, operational challenges, workflows, and industry-specific requirements is what creates successful digital transformation.
-With the right combination of experience + AI, we can deliver:
-✅ Faster requirement analysis
-✅ Early solution design and validation
-✅ More accurate and business-focused ERP implementation
-✅ Smarter automation strategies
-✅ Faster project delivery with improved quality
-Our experience helps us understand the business. AI helps us accelerate the process.
-This combination allows us to provide early, scalable, and future-ready ERP solutions for any industry while ensuring that technology solves real business problems, not just technical ones.
-We should stop thinking about "AI vs Humans" and start focusing on "AI + Humans."
-Because technology can accelerate the process, but experience determines the direction.
-AI may increase the speed of work. Experience ensures the work creates value.
-#AI #ERP #Odoo #DigitalTransformation #BusinessSolutions #Innovation #FutureOfWork #Technology #ExperienceMatters #BusinessGrowth</t>
+          <t>Abu Dhabi Emirate, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/marketing-manager-food-beverage-at-yas-plaza-hotels-by-aldar-hospitality-4426927907?position=59&amp;pageNum=0&amp;refId=XmMWvo8aKI%2BTS%2FC4M9t72A%3D%3D&amp;trackingId=iY0JY4PQQU8J4rPgd3cKQw%3D%3D</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>About Us
+Yas Plaza Hotels by Aldar Hospitality is a dynamic collection of six international hotels located in the heart of Yas Island, Abu Dhabi. This vibrant destination offers a seamless blend of relaxation, indulgence, and recreation, making it the ultimate gateway to the Yas Island experience...</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-03T04:20:27.000Z</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/odoodevelopers/permalink/2514487038992212/</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>Leasing Consultant</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>haus &amp; haus</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>📍 Track Your Fleet Directly from Odoo with Traccar Integration!
-Managing your fleet has never been easier.
-Our Fleet Traccar Tracking module seamlessly integrates Traccar with Odoo Fleet, allowing you to monitor your vehicles, routes, trips, and events—all from a single platform.
-✨ Key Features
-✅ Traccar Integration with Odoo Fleet
-✅ Live Vehicle Tracking
-✅ Trip &amp; Route History
-✅ Vehicle Event Logs
-✅ Google Maps &amp; OpenStreetMap Support
-✅ Device Summary &amp; Travel Analytics
-✅ Automatic Vehicle Synchronization
-✅ Multi-Vehicle Tracking
-✅ Easy Configuration
-Whether you're managing logistics, delivery vehicles, taxis, or service fleets, this module gives you complete visibility into your fleet operations.
-🚀 Available for Odoo 19
-👉 https://apps.odoo.com/apps/modules/19.0/ais_fleet_traccar_tracking
-💬 Have questions or need customization? Contact us—we're happy to help!
-#Odoo #Odoo19 #FleetManagement #VehicleTracking #GPS #Traccar #Logistics #Transportation #ERP #Fleet #BusinessSoftware #odooapps</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/leasing-consultant-at-haus-haus-4430451868?position=53&amp;pageNum=0&amp;refId=XmMWvo8aKI%2BTS%2FC4M9t72A%3D%3D&amp;trackingId=aNdhBaha9Yta%2F1PLiWYE1A%3D%3D</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Welcome to haus &amp;amp; haus. As one of Dubai's most trusted and reputable real estate agencies, we have an established record of achievement and service as well as expertise in Residential Sales and Leasing, Short Term and Holiday Rentals, Off Plan and Investments, Property Management and Commercial...</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-03T15:57:41.000Z</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1441170482773436/permalink/4805191446371306/</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>Junior Account Manager</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>WPP Production</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>هنبدأ  أول برزنتيشن لتعلم الOdoo الرد بنعم لتضاف 
-بالاضافه الي ملفات pdf المجانية</t>
+          <t>Dubai, Dubai, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/junior-account-manager-at-wpp-production-4438603189?position=54&amp;pageNum=0&amp;refId=XmMWvo8aKI%2BTS%2FC4M9t72A%3D%3D&amp;trackingId=olmubU82E0spZvMN4uqxcw%3D%3D</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>About WPP Production
+We are WPP Production - the unified global production company that brings together all of WPP's content producers, studios and craft experts into one connected organisation. We combine world-class human craft with next generation technology to originate, design, and deliver mul...</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-03T05:43:39.000Z</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/groups/1441170482773436/permalink/4804576636432787/</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>Brand Partnerships Lead</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Namshi.com</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>هنبدأ  أول برزنتيشن لتعلم الOdoo الرد بنعم لتضاف
-بالاضافه الي ملفات pdf المجانية</t>
+          <t>Dubai, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/brand-partnerships-lead-at-namshi-com-4429248642?position=55&amp;pageNum=0&amp;refId=XmMWvo8aKI%2BTS%2FC4M9t72A%3D%3D&amp;trackingId=jQgxJj%2FY06Orn5zTQ5ad3g%3D%3D</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>About Namshi:
+Are you ready to embark on an exciting journey in the world of beauty and e-commerce? Namshi, the #1 online fashion and beauty destination in the Middle East, is looking for talented individuals like you to join our dynamic team. We are a community built around young people who are ma...</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Real estate agent (Master Agency)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>fäm Properties Dubai</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Dubai, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/real-estate-agent-master-agency-at-f%C3%A4m-properties-dubai-4436053948?position=52&amp;pageNum=0&amp;refId=XmMWvo8aKI%2BTS%2FC4M9t72A%3D%3D&amp;trackingId=JyZjmY2t%2Fdk6IdcCpEhOdA%3D%3D</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>With almost two decades of operation fäm Properties is the largest and most technologically advanced real estate company ever built in Dubai. fäm Properties has created a fully holistic real estate ecosystem that provides clients, brokers, and employees with the best working and operating experienc...</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Influencer Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Salt</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Dubai, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/influencer-marketing-manager-at-salt-4433927134?position=48&amp;pageNum=0&amp;refId=XmMWvo8aKI%2BTS%2FC4M9t72A%3D%3D&amp;trackingId=Q8aWDKH3SDlGKne18VBW%2BA%3D%3D</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Influencer Marketing Manager / Campaign Manager 
+Dubai
+I'm working with one of Dubai's leading integrated marketing agencies, who are looking to hire an Arabic-speaking Influencer Marketing Manager to join their growing team.
+This is a fantastic opportunity to work across a portfolio of well-know...</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Content Creator (Social Media &amp; Performance Content) 🇦🇪</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>WONE ALTAVIA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Dubai, Dubai, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/content-creator-social-media-performance-content-%F0%9F%87%A6%F0%9F%87%AA-at-wone-altavia-4410955993?position=50&amp;pageNum=0&amp;refId=XmMWvo8aKI%2BTS%2FC4M9t72A%3D%3D&amp;trackingId=9O%2F4UEspbOXOCCr4h%2FfyEw%3D%3D</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>🚀 We're Hiring: Content Creator at WONE Digital Agency – Dubai 📍
+WONE Digital Marketing Agency | Dubai / Hybrid
+At WONE, we don’t create content for vanity metrics.
+We create content that builds brands, drives performance, and converts.
+We’re looking for a Content Creator who understands how to...</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Marketing and Communications Manager (Parts and Services)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Stellantis Middle East &amp; Africa</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Dubai, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/marketing-and-communications-manager-parts-and-services-at-stellantis-middle-east-africa-4430607983?position=51&amp;pageNum=0&amp;refId=XmMWvo8aKI%2BTS%2FC4M9t72A%3D%3D&amp;trackingId=7weMusgTMFMIa2IA0DcS6g%3D%3D</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Company Overview
+Build your brand. Tell your story. Make a lasting impact!
+Stellantis is a leading global automaker and mobility provider, delivering clean, connected, affordable, and safe mobility solutions. Our strength lies in the breadth of our iconic brand portfolio, the diversity and passio...</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Marketing Associate - Paid Media / Media Buyer</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Division50</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/jobs/view/marketing-associate-paid-media-media-buyer-at-division50-4437488010?position=49&amp;pageNum=0&amp;refId=XmMWvo8aKI%2BTS%2FC4M9t72A%3D%3D&amp;trackingId=jlx6UrM7I1oDUP8Jf4yX%2Fw%3D%3D</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>About The Role
+Division50 runs paid advertising that drives real leads for our clients. We're hiring a Marketing Associate / Media Buyer to plan, launch, and optimize campaigns across Meta and Google — someone who has personally owned budgets and hit cost targets.
+What You'll Do
+- Build, launch...</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E71"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>author_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>author_url</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>post_url</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>post_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-10 17:54:11</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Broné Ram</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/thetalentman?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAABp5DhABKUz2HC0QQN2ERHjqeM3-owZ5PME</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/thetalentman_hiring-dataengineering-analytics-activity-7481375226967003136-m-Cy?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>New Live Data Lead Role 🚀 🚀 🚀 
+🚨 We're helping fill one of the most important hires a company can make: 
+Its first ever data person.
+Not because of the title. Because of what it represents. 👇
+A fast-growing Saudi proptech company is building its first internal data function from scratch, and they're looking for the person to own it. Here's the full context, and why this role matters more than most.
+🏗️ THE COMPANY
+They're transforming how real estate transactions work in Saudi Arabia. Taking processes that have always been slow, manual and opaque, and making them fast, transparent and efficient through technology. As the business scales, data has moved from useful to strategic. It's now central to how they plan to grow.
+⚡ WHY THIS ROLE MATTERS
+Right now, engineering has built the data platform in Big Query, but there is a lot to do!
+This is not a dashboard job.
+You'll sit at the intersection of engineering, business and decision-making. You'll build the data foundation that lets every team, from Marketing and Sales to Operations and Leadership, make faster and smarter calls. You'll bring reporting that was outsourced to an external agency back in-house, giving the business real ownership and speed over its own numbers. And you'll set the standards: the architecture, the governance and the culture around how data is used across the org.
+In short, you're not joining a data team. You're founding one. 🚀
+🗓️ THE FIRST 90 DAYS
+✅ Take full ownership of the newly built data platform from engineering
+✅ Sit with Marketing, Sales and Operations to learn what they actually need
+✅ Ship the first production-ready datasets and dashboards
+✅ Rebuild the marketing reporting previously run by an outside agency
+✅ Become the person the whole company trusts with its data
+🧠 THE HONEST CHALLENGE
+This role combines what's often three jobs: data engineering, analytics engineering and business-facing reporting, all while building a brand new function from scratch. It suits someone who's as comfortable writing SQL as they are explaining insights to a non-technical exec, and who genuinely enjoys ownership and ambiguity.
+🎯 WHO WE'RE LOOKING FOR
+🔹 4 to 8+ years in Data Engineering, Analytics Engineering, BI or Data Analytics
+🔹 Strong SQL and hands-on data modelling and transformation
+🔹 Experience building modern data platforms and dashboards
+🔹 Fluent in both Arabic and English (non-negotiable) 🇸🇦
+🔹 Startup or high-growth experience strongly preferred
+🔹 Fintech, proptech or marketplace background is a real plus
+🔹 Based in Riyadh. On-site, reporting to the CTO 📍
+If you've ever wanted to build a company's data capability rather than inherit one, this is that rare chance. ✨
+💬 Interested, or know someone who'd be perfect? Comment below or DM me 👇
+#Hiring #DataEngineering #Analytics #Riyadh #SaudiArabia #Proptech #MENA #DataJobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-10 11:04:47</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Jeddah jobs, Makkah province</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/showcase/jeddah-jobs-makkah-province/posts</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/jeddah-jobs-makkah-province_httpsjobsrminecomjobsabusiness-development-specialist-activity-7481272200151474176-u7yx?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>#hiring Business Development Specialist
+Apply here: https://lnkd.in/gbWNB989
+Company Description Red Production is a full-service marketing, branding, media production, and business solutions company based in Jeddah, Saudi Arabia. We help businesses build powerful brands, create impactful marketing campaigns, deliver exceptional media production, and execute memorable corporate events.Our expertise spans Branding, Digital Marketing, Media Production, Corporate Events, Exhibitions, PR, Web &amp; App Development, AI Solutions, and Business Growth Strategies.As we continue to expand, were looking for a highly motivated Senior Business Development Executive to help drive our next stage of growth. Role Overview We are looking for a results-driven Business Development professional with a strong network in Saudi Arabia who has proven experience selling Marketing, Branding, Media Production, and Corporate Event solutions.This role is ideal for someone who understands the Saudi market, enjoys building long-term business relationships, and has the ability to generate new business opportunities and close high-value B2B deals. Key Responsibilities Business Development &amp; SalesIdentify, develop, and secure new business opportunities across the Saudi market.Build and maintain strong relationships with corporate clients and key decision-makers.Manage the complete sales cycle from prospecting and lead generation to negotiation and closing.Develop and maintain a healthy sales pipeline using CRM.Prepare professional proposals, presentations, quotations, and commercial offers.Achieve monthly and annual sales targets.Identify opportunities for upselling and cross-selling existing clients.Corporate Events &amp; Marketing SolutionsPromote Red Productions integrated services, including:BrandingDigital MarketingMedia ProductionCorporate EventsExhibitions &amp; BoothsPR ServicesWebsite &amp; App DevelopmentAI Business SolutionsWork closely with internal teams to deliver customized solutions that meet client objectives.Attend business meetings, networking events, exhibitions, and industry conferences to generate new opportunities.Client Relationship ManagementBuild long-term partnerships with clients.Maintain excellent customer satisfaction throughout the sales process.Follow up on opportunities and ensure successful project handovers.Coordinate with internal departments to ensure smooth project execution. Qualifications Minimum 5 years of experience in Business Development, Corporate Sales, or B2B Sales.Previous experience in a Marketing Agency, Advertising Agency, Branding Agency, Media Production Company, Event Management Company, or Exhibition Company is highly preferred.Strong understanding of the Saudi market.Existing network of corporate clients and decision-makers is highly preferred.Proven track record of achieving and exceeding sales targets.Excellent negotiation, presentation, and communication skills.Strong analytical and busin</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:04:47</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Growth Hub Marketing Agency</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/growthhubmarketingagency?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAAF4IkjoBTu0HaoGrk91_okUM8XAnLa4gq50</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/growthhubmarketingagency_socialmediamanager-socialmediamarketing-digitalmarketing-activity-7481257100770414592-rES-?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Grow Your Business with Professional Social Media Management!
+Looking to increase your brand awareness, generate quality leads, and boost your online presence? Growth Hub Marketing Agency (GHMA) provides complete social media management solutions designed to help businesses grow faster and achieve measurable results.
+ Our Services:
+ Facebook Page Management
+ Instagram Growth
+ Content Creation
+ Meta Ads Management
+ Social Media Strategy
+ Audience Engagement
+ Brand Awareness Campaigns
+ Lead Generation
+ Business Growth Solutions
+Whether you're a startup, local business, eCommerce store, restaurant, real estate agency, cleaning company, healthcare provider, or corporate brand, we create powerful social media strategies that drive real results.
+ Serving Clients Worldwide, including Saudi Arabia, UAE, Qatar, Kuwait, Bahrain, Oman, United Kingdom, United States, Canada, Australia, and more.
+ Contact us today and let's grow your business with high-performing social media marketing.
+WhatsApp: 
+0322 6174935
+#SocialMediaManager
+#SocialMediaMarketing
+#DigitalMarketing
+#MetaAds
+#FacebookMarketing
+ #InstagramMarketing #ContentCreation #Branding #BusinessGrowth #LeadGeneration #FacebookAds #InstagramAds #MarketingAgency #GrowthHub #GHMA #OnlineMarketing #SmallBusiness #Startup #MarketingStrategy #SocialMediaManagement #SaudiArabia #UAE #Qatar #Kuwait #Bahrain #Oman #UKBusiness #USA #Canada #Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:04:05</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Growth Hub Marketing Agency</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/growthhubmarketingagency?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAAF4IkjoBTu0HaoGrk91_okUM8XAnLa4gq50</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/growthhubmarketingagency_metaads-facebookads-instagramads-activity-7481256924613660672-0VXd?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Scale Your Business with High-Converting Meta Ads!
+Are you looking to generate more leads, increase sales, and maximize your return on ad spend? Growth Hub Marketing Agency (GHMA) specializes in creating and managing high-performing Facebook &amp; Instagram advertising campaigns that help businesses grow faster.
+Our Professional Meta Ads Services
+ Facebook Ads Management
+ Instagram Ads Management
+ Lead Generation Campaigns
+ Sales &amp; Conversion Campaigns
+ E-commerce Ads
+ Local Business Advertising
+ Website Traffic Campaigns
+ Custom Audience Targeting
+ Remarketing &amp; Retargeting Ads
+ Pixel Setup &amp; Conversion Tracking
+ Campaign Optimization
+ ROAS Optimization
+Whether you own an eCommerce store, restaurant, real estate agency, medical clinic, cleaning company, gym, salon, law firm, or any local business, we create data-driven advertising strategies that deliver measurable results.
+ Why Choose GHMA?
+ High-Converting Ad Campaigns
+ Advanced Audience Targeting
+ Lower Cost Per Result
+ Increased Sales &amp; Qualified Leads
+ Professional Campaign Management
+ Transparent Performance Reporting
+ Serving Businesses Worldwide, including Saudi Arabia, UAE, Qatar, Kuwait, Bahrain, Oman, United Kingdom, United States, Canada, and Australia.
+ Limited Time Offer – Get 30% OFF!
+ Message us today for a FREE consultation and let us grow your business with profitable Meta Ads.
+ WhatsApp: 
+0322 6174935
+ Email: msaadmalik467@gmail.com
+#MetaAds
+#FacebookAds
+#InstagramAds
+#MetaAdsExpert
+#FacebookMarketing
+#InstagramMarketing
+#LeadGeneration
+#DigitalMarketing
+#PerformanceMarketing
+#PaidAdvertising
+#ConversionAds
+ #SalesFunnel #BusinessGrowth #SocialMediaMarketing #MarketingAgency #EcommerceMarketing #LocalBusinessMarketing #OnlineAdvertising #GrowthHub #GHMA #SaudiArabia #UAE #Qatar #Kuwait #Bahrain #Oman #UKBusiness #USABusiness #CanadaBusiness #AustraliaBusiness</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:03:30</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Growth Hub Marketing Agency</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/growthhubmarketingagency?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAAF4IkjoBTu0HaoGrk91_okUM8XAnLa4gq50</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/growthhubmarketingagency_digitalmarketing-digitalmarketingexpert-digitalmarketingagency-activity-7481256774780506112-kFWz?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Grow Your Business with Professional Digital Marketing Services
+Looking to increase your online presence, generate high-quality leads, and grow your business? Growth Hub Marketing Agency (GHMA) provides result-driven digital marketing solutions designed to help businesses achieve measurable growth and long-term success.
+Whether you're a startup, small business, eCommerce store, restaurant, real estate agency, healthcare provider, cleaning company, salon, law firm, or corporate brand, we create customized marketing strategies that deliver real results.
+ Our Professional Services
+ Lead Generation
+ Content Marketing
+ Brand Management
+ Social Media Marketing
+ Meta Ads Management
+ Reels &amp; Short Video Marketing
+Why Choose GHMA?
+ Customized Digital Marketing Strategy
+ High-Quality Lead Generation
+ Increased Brand Awareness
+ Higher Engagement &amp; Sales
+ ROI-Focused Marketing Campaigns
+ Professional Reporting &amp; Performance Tracking
+ Serving businesses worldwide, including Saudi Arabia, UAE, Qatar, Kuwait, Bahrain, Oman, United Kingdom, United States, Canada, and Australia.
+ Let us help you attract more customers, increase conversions, and grow your business with powerful digital marketing strategies.
+ Book Your Free Consultation Today!
+ WhatsApp: 
+0322 6174935
+ Email: msaadmalik467@gmail.com
+#DigitalMarketing
+#DigitalMarketingExpert
+#DigitalMarketingAgency
+#GrowthHub
+#GHMA
+#SocialMediaMarketing
+#MetaAds
+#FacebookAds
+ #InstagramAds #LeadGeneration #ContentMarketing #BrandManagement #BusinessGrowth #OnlineMarketing #MarketingStrategy #DigitalAdvertising #SmallBusiness #Startup #EcommerceMarketing #LocalBusiness #MarketingAgency #SEO #GoogleAds #ReelsMarketing #BusinessSuccess #SaudiArabia #UAE #UKBusiness #USABusiness #CanadaBusiness</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-10 09:01:35</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Overseas Manpower recruitment Agency Pakistan Islamabad</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/overseas-manpower-recruitment-agency-pakistan-islamabad-5abb09178?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAACoqxBMBb45qNjTZ3YmT0VboPYFTJm9w3y4</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/overseas-manpower-recruitment-agency-pakistan-islamabad-5abb09178_site-is-undergoing-maintenance-activity-7481241193972940800-RqQ3?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Are you planning to source professional, skilled and unskilled Manpower from Pakistan?
+Looking for a reliable global partner to join you in the recruitment process?
+If yes, then please consider Neom recruitment Group LIC# OP&amp;HRD/4649/RWP. We are providing quality and dedicated manpower in Middle East for the past 20 Years.
+Countries where we are providing Manpower:
+Kingdom of Saudi Arabia – Sultanate of OMAN – State of QATAR – United Arab Emirates –Kingdom of Bahrain–
+Our Offices In Karachi Islamabad And Lahore
+MANPOWER CATEGORIES [You Can Ask For Any Category]
+Agriculture, Assistant Technician and Technical Helper, Doctors, Nurses, Para Medical Staff, Lab Technicians, Accountant, Auditors, Finance Managers, HR Manager, Marketing Managers, Biomedical Engineers, Chemical Engineers, Oil &amp; Gas Engineers, Electrical Engineer, Electronic Engineers, Mechanical Engineer, Telecom Engineers, Civil Engineer, Civil Architecture, IT Engineers, Network Engineers, Software Engineers, HVAC Engineers, Auto Cad Operators, Bankers, Sales Man, Automobile Technicians, Blacksmiths, Carpenters, Cleaner, Cook, Crane Operators, Driver, Electricians, Equipment and Machine Operators, Fabricators, Fitters, Foreman, General Worker, Hotel Manager, Hotel Boy, waiters, House made, Lagers, Masson, Mechanics, Nurse, Office Boy, Security Guards, Safety Officers, Secretary, Painters, Plumbers, Drivers, Scaffold, Skilled / Semiskilled – Steel-fixers, Tailoring, Technicians, Tiles mystery, Tool Keepers, Welders, and Unskilled Laborers (All type) and all kinds of construction workers.
+For Manpower Requirements Email 
+Email : Ali.neomrecruitmentgroup@gmail.com
+Website https://lnkd.in/dH9VFktq
+Mobile 00923707530125</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-10 09:00:23</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Virtual Growth Recruitment</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/virtual-growth-recruitment/posts</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/virtual-growth-recruitment_remotejobs-hiringnow-workfromhome-activity-7481240894101352448-khGk?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Digital Marketing Specialist (Part-Time | Remote)
+📍 Location: Remote
+About Nourline
+Nourline is a digital agency specializing in website design, e-commerce solutions, branding, SEO, and digital marketing. We help businesses, particularly in Saudi Arabia and the GCC, build a strong online presence and achieve measurable business growth.
+We are looking for a results-driven Digital Marketing Specialist to join our team on a part-time, fully remote basis. This role focuses on developing and executing performance marketing strategies that generate qualified leads and drive business growth—not just managing social media.
+Key Responsibilities
+Develop and execute comprehensive digital marketing strategies.
+Plan, launch, manage, and optimize campaigns across Google Ads and Meta Ads.
+Experience with LinkedIn Ads, TikTok Ads, or Snapchat Ads is a strong advantage.
+Identify the most effective marketing channels for different services and target markets.
+Optimize landing pages to improve conversion rates.
+Track and analyze campaign performance using Google Analytics 4, Google Tag Manager, and Meta Pixel.
+Improve campaign performance, reduce cost per acquisition (CPA), and maximize ROI.
+Conduct ongoing A/B testing to improve results.
+Prepare regular performance reports with actionable insights and recommendations.
+Stay up to date with the latest digital marketing trends and best practices.
+Requirements
+Proven experience in digital marketing with measurable results.
+Strong hands-on experience with Google Ads and Meta Ads.
+Experience with LinkedIn Ads, TikTok Ads, or Snapchat Ads is preferred.
+Experience marketing services, especially in the Saudi or GCC market.
+Previous experience with web design agencies, digital marketing agencies, e-commerce companies, or IT companies targeting the GCC is highly preferred.
+Good understanding of SEO, landing page optimization, Google Analytics 4, Google Tag Manager, and Meta Pixel.
+Strong analytical, strategic thinking, and problem-solving skills.
+Excellent campaign planning and optimization skills.
+Ability to work independently in a fully remote environment and manage priorities effectively.
+Job Details
+Employment Type: Part-Time
+Location: Remote
+Work Mode: Fully Remote
+Target Market: Saudi Arabia &amp; GCC
+To Apply
+Please send the following to info@nourline.com:
+Your CV
+Portfolio (if available)
+Examples of campaigns you have managed with measurable results
+Expected salary
+Expected working hours
+Earliest available start date
+Applications without the required information will not be considered. Preference will be given to candidates who can demonstrate documented campaign results, such as qualified leads, CPA.
+#RemoteJobs
+#HiringNow
+#WorkFromHome 
+#RemoteWork
+#JobSearch 
+#CareerOpportunity 
+#NowHiring 
+#JobOpening 
+#DataEntry 
+#Logistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-10 08:02:08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Paul Wallis</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/wallispaul?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAAAAAZbIBiLeMnh6Fuoi_u4SClWdQ8A4VDQA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/wallispaul_granitemena-leadership-growth-activity-7481226233674883072-h5-Q?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>From Dublin to Dubai
+A huge congratulations to my co-founder, Lionel Laulhé, on his appointment as Chief Growth Officer of Granite MENA.
+When we started Granite MENA, there were just two of us, a whiteboard, a small office, too much coffee and absolutely no shortage of optimism.
+We started with one simple belief.
+Businesses across the Middle East deserved something different.
+Not another agency selling projects. Not another company pushing AI because it was fashionable.
+But a genuine growth partner, combining strategy, creativity, marketing, data, digital transformation and AI to solve real commercial challenges.
+We also wanted to build a business based on fairness, transparency and trust.
+Our philosophy has always been simple.
+"We love leaving clients with a prototype, not just a PowerPoint"c.
+Something they can see, experience and test.
+That thinking led to @TAAMAI, our AI-powered digital studio, where strategy, creativity and technology come together to bring ideas to life in days rather than months.
+Eighteen months later we've grown from two people and a whiteboard into a team of 16 incredible people, supported by outstanding partners, with a Saudi Arabia office opening soon.
+Looking back, choosing Lionel Laulhé as my co-founder is one of the smartest business decisions I've ever made.
+I'm usually the one out with clients throwing the bear into the room.
+Lionel with the team are the ones who somehow tame it, build it and make it happen.
+Most of the time we agree, but we challenge each other constantly, bringing different perspectives that make the business stronger.
+Behind this new title is someone with enormous integrity, an incredible work ethic and a genuine commitment to doing the right thing for our clients, our people and our business.
+To our team, clients, partners, shareholders (Colin Meagle, Colm Piercy) and GRANITE - Global Digital Agency, thank you for believing in the vision.
+We're proud of what we've built. But it still feels like Day One.
+Congratulations, my friend. I couldn't have asked for a better co-founder for this journey.
+Now there's just one thing we'll never agree on...
+Who lifts the World Cup. Lionel says France. I say England.
+Let's see how long this post stays relevant... 😄⚽
+From Dublin to Dubai... and now from Dubai to Riyadh. 😊
+#GraniteMENA #Leadership #Growth #AI #DigitalTransformation #SaudiArabia #NeverStandingStill</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-09 20:49:58</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mehvish Haroon</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mehvishharoon?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAAEGkDUUBsmA-Iwgkwl483T3YwBziFrJa7QQ</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/mehvishharoon_seo-linkbuilding-guestposting-activity-7481057076031713280-Cd-i?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>🚀 Need High-Quality Backlinks That Support Long-Term SEO Growth?
+If you're a business owner, SEO agency, affiliate marketer, or website owner looking to improve your online visibility, we provide professional link-building services tailored to your SEO strategy.
+We focus on delivering high-quality backlinks through manual outreach and niche-relevant websites to help strengthen your website's authority and organic presence.
+Our SEO &amp; Link Building Services
+🔹 Guest Posts (DA 30–90+)
+🔹 Niche Edits (Link Insertions)
+🔹 Profile Backlinks
+🔹 Web 2.0 Backlinks
+🔹 Social Bookmarking
+🔹 Directory Submissions
+🔹 Blog Comment Backlinks
+🔹 EDU &amp; GOV Backlinks
+🔹 Premium PBN Backlinks (Available on Request)
+🔹 Local Citations
+🔹 Press Release Distribution
+🔹 Article Submission
+🔹 Forum Backlinks
+🔹 Custom Link Building Campaigns
+Industries We Serve
+🎰 Casino &amp; iGaming
+🎯 Sports Betting
+💰 Cryptocurrency &amp; Blockchain
+📊 Forex &amp; Finance
+🛒 E-commerce
+💻 SaaS &amp; Technology
+🏥 Healthcare
+⚖️ Legal Services
+🏠 Real Estate
+🎮 Gaming
+📲 Mobile Apps &amp; APK
+🎓 Education
+✈️ Travel
+🔞 Adult
+…and many more.
+Global SEO Solutions
+We work with businesses targeting:
+🇺🇸 USA • 🇬🇧 UK • 🇨🇦 Canada • 🇦🇺 Australia • 🇳🇿 New Zealand • 🇦🇪 UAE • 🇸🇦 Saudi Arabia • 🇶🇦 Qatar • 🇰🇼 Kuwait • 🇴🇲 Oman • 🇧🇭 Bahrain • 🇸🇬 Singapore • 🇲🇾 Malaysia • 🇮🇳 India • 🇵🇰 Pakistan • 🇩🇪 Germany • 🇫🇷 France • 🇪🇸 Spain • 🇮🇹 Italy • 🇳🇱 Netherlands • 🇨🇭 Switzerland • 🇸🇪 Sweden • 🇳🇴 Norway • 🇩🇰 Denmark • 🇮🇪 Ireland • 🇵🇱 Poland • 🇯🇵 Japan • 🇰🇷 South Korea and many other international markets.
+Why Clients Choose Us
+✔ Manual &amp; Ethical Link Building
+✔ High-Authority, Niche-Relevant Websites
+✔ Customized Campaigns for Every Project
+✔ Transparent Reporting
+✔ Competitive Pricing
+✔ On-Time Delivery
+✔ Long-Term Business Relationships
+Whether you need a single guest post or a complete off-page SEO campaign, we're ready to help.
+📩 Let's discuss your project and create a customized link-building strategy for your website.
+📧 Email: infomeshimarketing@gmail.com
+💬 WhatsApp: https://t.ly/8xjbt
+📘 Facebook: https://lnkd.in/dWF5kre9
+💼 LinkedIn: https://lnkd.in/dFfk7u4z
+✈️ Telegram: https://lnkd.in/drEJ6y7N
+🌐 Website: https://lnkd.in/dnSGZYaF
+#SEO #LinkBuilding #GuestPosting #Backlinks #OffPageSEO #DigitalMarketing #ContentMarketing #SearchEngineOptimization #Marketing #BusinessGrowth #SEOServices #GuestPost #Agency #Ecommerce #SaaS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-09 17:48:47</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Asmaa Mostafa</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/asmaa-mostafa-developer?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAADmFItkBX9aovinSlnXsjGglZczmtlI0jQo</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/feed/update/urn:li:groupPost:14557939-7480894566632558592?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Digital Marketing Specialist (Part-Time | Remote)
+📍 Location: Remote
+About Nourline
+Nourline is a digital agency specializing in website design, e-commerce solutions, branding, SEO, and digital marketing. We help businesses, particularly in Saudi Arabia and the GCC, build a strong online presence and achieve measurable business growth.
+We are looking for a results-driven Digital Marketing Specialist to join our team on a part-time, fully remote basis. This role focuses on developing and executing performance marketing strategies that generate qualified leads and drive business growth—not just managing social media.
+Key Responsibilities
+Develop and execute comprehensive digital marketing strategies.
+Plan, launch, manage, and optimize campaigns across Google Ads and Meta Ads.
+Experience with LinkedIn Ads, TikTok Ads, or Snapchat Ads is a strong advantage.
+Identify the most effective marketing channels for different services and target markets.
+Optimize landing pages to improve conversion rates.
+Track and analyze campaign performance using Google Analytics 4, Google Tag Manager, and Meta Pixel.
+Improve campaign performance, reduce cost per acquisition (CPA), and maximize ROI.
+Conduct ongoing A/B testing to improve results.
+Prepare regular performance reports with actionable insights and recommendations.
+Stay up to date with the latest digital marketing trends and best practices.
+Requirements
+Proven experience in digital marketing with measurable results.
+Strong hands-on experience with Google Ads and Meta Ads.
+Experience with LinkedIn Ads, TikTok Ads, or Snapchat Ads is preferred.
+Experience marketing services, especially in the Saudi or GCC market.
+Previous experience with web design agencies, digital marketing agencies, e-commerce companies, or IT companies targeting the GCC is highly preferred.
+Good understanding of SEO, landing page optimization, Google Analytics 4, Google Tag Manager, and Meta Pixel.
+Strong analytical, strategic thinking, and problem-solving skills.
+Excellent campaign planning and optimization skills.
+Ability to work independently in a fully remote environment and manage priorities effectively.
+Job Details
+Employment Type: Part-Time
+Location: Remote
+Work Mode: Fully Remote
+Target Market: Saudi Arabia &amp; GCC
+To Apply
+Please send the following to info@nourline.com:
+Your CV
+Portfolio (if available)
+Examples of campaigns you have managed with measurable results
+Expected salary
+Expected working hours
+Earliest available start date
+Applications without the required information will not be considered. Preference will be given to candidates who can demonstrate documented campaign results, such as qualified leads, CPA, or ROAS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-09 16:38:56</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mohamed Tarek</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/m-tarek98?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAAC1gRv0Bw-vfff-Cl6Or6HQHVx1aB6NUxUQ</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/m-tarek98_hiring-digitalmarketing-saudimarket-activity-7480993900401242113-vpuC?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>We’re Hiring: Digital Marketing Specialist (Saudi Market Focus) 
+Boost Marketing Agency is looking for a results-driven Digital Marketing Specialist who knows the Saudi market inside out 
+If you understand Saudi consumer behavior, digital trends, and cultural insights, we want you on our team.
+📍 Location: Mohandessin, Giza, Egypt (On-site) 
+🕒 Type: Full-time 
+💼 Experience: 2–4 years in digital marketing
+Key Responsibilities:
+Manage &amp; optimize campaigns across Google, Meta, Snapchat, and TikTok.
+Develop content and social media strategies tailored to the Saudi audience.
+Execute SEO &amp; SEM strategies (Arabic &amp; English).
+Analyze performance data to drive campaign growth.
+What We’re Looking For:
+Solid experience with regional/Saudi marketing campaigns.
+Fluency in both Arabic and English.
+Hands-on expertise with major ad platforms and analytics tools.
+📩 Ready to apply? Send your CV to: m.tarek@ctc-ksa.co
+#Hiring #DigitalMarketing #SaudiMarket #MarketingJobs #GizaJobs #JobOpportunity</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-09 15:16:57</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GenAI Hub</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/genai-consultant/posts</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/genai-consultant_were-hiring-social-media-specialist-activity-7480973269186117633-2SE6?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>🚀 We're Hiring: Social Media Specialist
+GenAI Agency is looking for a Social Media Specialist to join our team in Maadi.
+Requirements: 
+✔️ Experience in Social Media Management.
+ ✔️ Previous experience in the medical sector. 
+✔️ Strong understanding of the Saudi market. 
+✔️ Ability to create content plans and engaging marketing content.
+📍 Full-time | On-site  Location: Maadi, Cairo
+📧 Send your CV and portfolio</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-09 13:38:18</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dana Refai</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/danarefai?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAAAg2uCIBeSgSTa3yokyIT2ECQbz9dLlzbK4</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/danarefai_clientservicing-freshgraduate-hiring-activity-7480948445961261056-V_nN?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>"Great campaigns don't just happen in the creative room. They happen because someone in the room made sure the client trusted the process."
+📌Leo Riyadh is looking for a fresh graduate to join our Client Servicing team.
+What we need:
+ ✅ Saudi National based in Riyadh
+ ✅ Recent graduate (0–1 year of experience) with a Business, Marketing, or Communications background
+ ✅ Fluent in Arabic and English
+ ✅ Any internship/COOP experience (agency, corporate, or otherwise) is a plus
+ ✅ Eager to learn how the business side of advertising really works
+If you are ready to start your career at one of the region's biggest agencies - apply on the link below.
+#ClientServicing #FreshGraduate #Hiring #Riyadh #SaudiArabia #LeoBurnett #AccountManagement #NowHiring #EntryLevelJobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-09 12:16:14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HATOON A.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hatoon-a-00a339164?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAACc0U8oBjbNXhLKwCbu9RiaYEVraD1ZLgPg</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/activity-7480927792331943936-L7hy?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>😊Hello hello….
+Build Your Team with the Right Talent.
+At our recruitment agency, we connect organizations with highly qualified Saudi and international professionals across all industries and job functions.
+We provide recruitment solutions for:
+• Hospitality &amp; Hotels
+• Construction &amp; Engineering
+• Oil &amp; Gas
+• Healthcare
+• Information Technology (IT)
+• Finance &amp; Banking
+• Human Resources
+• Sales &amp; Marketing
+• Retail &amp; FMCG
+• Manufacturing
+• Logistics &amp; Supply Chain
+• Facilities Management
+• Aviation
+• Real Estate
+• Government &amp; Private Sector
+• Mega Projects &amp; Infrastructure
+• And many more.
+Our candidates are carefully selected, professionally trained, and continuously developed to meet the highest industry standards. We don’t just recruit 
+we invest in talent through ongoing training, performance follow up, and continuous support to ensure long-term success.
+Whether you’re hiring Fresh Graduates, Entry Level (Joiners), Specialists, Supervisors, Managers, Directors, or Senior Executives, we deliver the right talent tailored to your business needs.
+📩 Looking for exceptional talent? Let’s connect and discuss how we can support your recruitment goals. 😎
+#Recruitment #TalentAcquisition #Hiring #StaffingSolutions #ExecutiveSearch #SaudiTalent #GlobalTalent #HumanResources #BusinessGrowth #WorkforceSolutions #Leadership #Careers #SaudiArabia #GCC #HiringNow</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-09 10:11:50</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Nourline</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nourline/posts</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/nourline_digital-marketing-specialist-part-time-activity-7480896487078612992-RNyv?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Digital Marketing Specialist (Part-Time | Remote)
+📍 Location: Remote
+About Nourline
+Nourline is a digital agency specializing in website design, e-commerce solutions, branding, SEO, and digital marketing. We help businesses, particularly in Saudi Arabia and the GCC, build a strong online presence and achieve measurable business growth.
+We are looking for a results-driven Digital Marketing Specialist to join our team on a part-time, fully remote basis. This role focuses on developing and executing performance marketing strategies that generate qualified leads and drive business growth—not just managing social media.
+Key Responsibilities
+Develop and execute comprehensive digital marketing strategies.
+Plan, launch, manage, and optimize campaigns across Google Ads and Meta Ads.
+Experience with LinkedIn Ads, TikTok Ads, or Snapchat Ads is a strong advantage.
+Identify the most effective marketing channels for different services and target markets.
+Optimize landing pages to improve conversion rates.
+Track and analyze campaign performance using Google Analytics 4, Google Tag Manager, and Meta Pixel.
+Improve campaign performance, reduce cost per acquisition (CPA), and maximize ROI.
+Conduct ongoing A/B testing to improve results.
+Prepare regular performance reports with actionable insights and recommendations.
+Stay up to date with the latest digital marketing trends and best practices.
+Requirements
+Proven experience in digital marketing with measurable results.
+Strong hands-on experience with Google Ads and Meta Ads.
+Experience with LinkedIn Ads, TikTok Ads, or Snapchat Ads is preferred.
+Experience marketing services, especially in the Saudi or GCC market.
+Previous experience with web design agencies, digital marketing agencies, e-commerce companies, or IT companies targeting the GCC is highly preferred.
+Good understanding of SEO, landing page optimization, Google Analytics 4, Google Tag Manager, and Meta Pixel.
+Strong analytical, strategic thinking, and problem-solving skills.
+Excellent campaign planning and optimization skills.
+Ability to work independently in a fully remote environment and manage priorities effectively.
+Job Details
+Employment Type: Part-Time
+Location: Remote
+Work Mode: Fully Remote
+Target Market: Saudi Arabia &amp; GCC
+To Apply
+Please send the following to info@nourline.com:
+Your CV
+Portfolio (if available)
+Examples of campaigns you have managed with measurable results
+Expected salary
+Expected working hours
+Earliest available start date
+Applications without the required information will not be considered. Preference will be given to candidates who can demonstrate documented campaign results, such as qualified leads, CPA, or ROAS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-10 15:01:54</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Muhammad Bilal</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/xbilalch?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAAGLH4lUB4TxlGwiA_uWtzQBUWlmVEMemTT0</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/xbilalch_dubairealestate-uaerealestate-leadgeneration-activity-7481331872237744129-VBjw?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Why 95% of UAE Real Estate Leads "Ghost" Your Agents (And How to Fix It) 🇦🇪📉
+Every real estate agency leader in the UAE knows this frustration.
+Your marketing team delivers a fresh batch of leads.
+Your agents get excited.
+They start making calls.
+The result?
+❌ "Wrong number."
+❌ "I never filled out a form."
+❌ WhatsApp blue ticks... with zero reply.
+In a market as fast-paced as Dubai and Abu Dhabi, poor lead quality isn't just frustrating—it's costing agencies premium commissions while burning out their best salespeople.
+Here's the reality:
+The agencies winning today aren't generating more leads. They're generating better conversations.
+If you're targeting high-net-worth investors (HNWIs) looking for luxury off-plan developments or ready-to-move properties, traditional Facebook instant forms are no longer enough.
+The Shift: Intent-Driven Lead Generation
+The best-performing agencies focus on quality before quantity.
+✅ Ditch Auto-Fill Forms
+If someone can become a "lead" in two clicks without reading your offer, they probably weren't interested in the first place.
+✅ Qualify Every Prospect
+Ask meaningful questions before submission:
+• Budget range
+• Investment timeline
+• Preferred communities (Downtown Dubai, Dubai Marina, Palm Jumeirah, etc.)
+✅ Build a Structured Follow-Up System
+Successful agencies don't rely on one phone call. They nurture prospects through multiple touchpoints using data-driven follow-up.
+---
+Lead generation is only the first step.
+The real competitive advantage comes from turning qualified prospects into meaningful sales conversations—and ultimately, closed transactions.
+That's exactly what LeadAura is focused on:
+Helping real estate businesses shift from chasing more leads to attracting high-intent opportunities.
+I'm looking forward to connecting with more professionals across the UAE real estate industry—agents, team leaders, sales managers, managing directors, and founders—to learn, exchange ideas, and contribute to the industry's growth.
+👇 If you're in UAE real estate, I'd love to connect.
+What's the biggest lead-generation or marketing challenge your team is trying to solve in 2026?
+Let's discuss in the comments.
+#DubaiRealEstate #UAERealEstate #LeadGeneration #RealEstateMarketing #MetaAds #GoogleAds #DigitalMarketing #PropertyMarketing #DubaiProperty #BusinessGrowth #LeadAura</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-10 13:35:59</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ru Zhang</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lifer-realty?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAAEJ97rcBxGE-ry1Wb15zbiwxB1M-bn9fnNc</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/lifer-realty_liferrealty-wearehiring-dubaijobs-activity-7481310249220636672-w6f3?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>✔️ We’re Hiring at Lifer Realty Co.!
+Established in 2022, Lifer Realty Co. is an award-winning real estate agency in Dubai, supported by a diverse team of brokers from more than seven nationalities. We are proud to create a professional, flexible, and friendly working environment where both our clients and employees feel valued and supported.
+As we continue to grow and expand into our new office in Business Bay, Dubai, we are looking for experienced and motivated professionals to join our team.
+Current Vacancies:
+ Market Analyst – AED 10,000 salary
+ Leasing Agent – Salary plus commission
+ Experienced Real Estate Broker – Commission-based role with up to 80% commission
+We provide visa support, attractive salary or commission packages depending on the role, marketing support, professional training, listing access, and other employee benefits.
+Join a growing company that values teamwork, professional development, flexibility, and long-term success.
+📍 Location: Business Bay, Dubai
+ 🌐 Website: Lifer.ae
+ 📞 To Apply: Share your CV to 0542477315
+#LiferRealty #WeAreHiring #DubaiJobs #RealEstateJobs #DubaiRealEstate #MarketAnalyst #LeasingAgent #RealEstateBroker #BusinessBay #HiringDubai #UAEJobs #RealEstateCareers #JoinOurTeam #PropertyJobs #DubaiCareers</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-10 13:01:34</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Varun Abrol</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/varun-abrol-a5065015b?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAACZcUtwBL3Qaig12xJxf3DO7GXn6SG4Bb8E</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/varun-abrol-a5065015b_hiring-internship-socialmediamarketing-activity-7481301587479461888-ZxFu?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Street Origins is on the lookout for a creative and driven Social Media Marketing Intern to join our team in Dubai!
+. If you live and breathe social media, this one's for you. 👇
+What you'll be doing:
+📱 Planning and executing daily content across Instagram, TikTok &amp; more
+🌍 Managing our social media handles across different countries
+🤝 Coordinating with our social media agency on campaigns and content
+✍️ Drafting captions, selecting visuals, and keeping our brand voice on point
+📊 Monitoring engagement and compiling performance reports
+💡 Brainstorming campaign ideas and researching the latest trends
+What we're looking for:
+✅ Skills in social media marketing, digital marketing &amp; content creation
+✅ Strong written and verbal communication
+✅ Familiarity with major platforms, analytics &amp; digital trends
+✅ Studies in Marketing, Communications, Media, or related field (preferred)
+✅ Ability to work on-site in Dubai
+You'll get hands-on experience, real mentorship, and the chance to help shape a brand from the inside. 🚀
+📩 Interested? Apply now or send your CV and LinkedIn Profiles to Varuna@ghuroobnet.com
+#Hiring #Internship #SocialMediaMarketing #DigitalMarketing #DubaiJobs #MarketingInternship #StreetOrigins #DubaiCareers</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-10 12:59:26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>🤖 Nasser Oudjidane</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nasser-oudjidane?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAAA90x7EBBSSCp6SCR1Js0tS2nBHv9odC8K0</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/nasser-oudjidane_were-hiring-a-customer-success-lead-for-activity-7481301053141848065-_ZQD?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>We're hiring a Customer Success Lead for EMEA, based in Dubai.
+Google and Meta are becoming black boxes. Performance Max and Advantage+ don't give you levers anymore, just a ROAS target. And that target is a floor: the platform only has to clear it across your whole budget to keep you spending, so it delivers the minimum performance you'll accept, and no more.
+The one lever you keep is the signal you feed it: the conversions you tell the platform to value. It buys the cheapest traffic that clears that signal, so if junk is polluting it, junk is what it optimizes toward.
+Tapper is the quality traffic layer for performance marketing. We work inside the walled gardens and close the loop between traffic quality and platform optimization, so the algorithm learns from real users instead of bots, click farms and junk. We prove the incremental lift with the platforms' own native A/B tests. It all runs on Forge, our platform.
+With the signal clean, marketers are left with the one job that actually matters: deciding what a valuable customer looks like and feeding that back to the platforms. That's what this role owns.
+You'd run a book of 50 clients across the region and support the team on our biggest global accounts. Day to day, that means onboarding, reporting, QBRs and putting out fires. The traffic quality layer runs automatically, so your job is the part that takes a human: helping each client get that signal right, showing them what we caught and what it changed, and keeping demanding marketing teams confident in the numbers.
+We're lean and flat. When a client asks for something, whether it's a feature, an optimization or a model change, you take it straight to the engineer, analyst or data scientist who owns it, and it gets built.
+I'm looking for someone from a performance marketing agency, deep in paid search and paid social. You know Google, Meta and TikTok back to front, right down in the weeds, and you can hold a room with our biggest enterprise clients. You're not afraid of getting on a plane to visit customers, late nights, or grinding with the team when it gets tough.
+The link's in the comments. If it is you, DM me and tell me why you're a fit or get someone I trust to refer you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-10 11:31:53</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Abdullah Nasir</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/abdullah-nasir-775595b0?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAABeUOwkBNPzenRQdpNWolmT4AM7MGfBNCAY</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/abdullah-nasir-775595b0_if-i-had-a-dime-for-every-time-someone-said-activity-7481279017153806336-hJzB?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>If I had a dime for every time someone said "No" to me, I'd probably be a millionaire by now. 😉
+No, when I decided to step away from my family business.
+No, when I chose to build a career beyond borders.
+No, when I moved my operations to Dubai.
+No, when I started G12.
+And another no, when I decided to build a marketing agency in Karachi.
+Looking back, it's funny how the loudest applause usually comes after you've made it. But I don't blame the people who said no. Most of them weren't trying to discourage me. They genuinely believed they were protecting me. Because when you choose uncertainty over comfort, the safer option almost always sounds like the wiser one.
+But every meaningful decision I've made in my life started with belief, not validation.
+Looking at these photos today, I don't just see an office coming together.
+I see a season of my life where almost every decision felt uncomfortable. A season where progress was hard to measure, where every small win came with a new challenge, and where the vision made a lot more sense to me than it did to anyone else.
+The truth is, I never set out to prove anyone wrong.
+I simply wanted to build something I believed in.
+Today, G12 Digital has a footprint in Pakistan.
+A few years ago, this was just another idea that many people didn't believe in. Had I let someone else's "No" become my own, this would've never been possible.
+But I'm not done yet.
+The rest… What Allah wills.
+P.S. Sharing these raw photos for anyone who's in the thick of building something. Keep going. The messy part doesn't last forever.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:05:07</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>sean genon</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sean-genon?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAAAlCBUQBDSMwO6WUS96yQ-94Xm1VQjRcwys</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/sean-genon_hiring-dubai-advertising-activity-7481257184790585344-JFOK?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>🔊 🔊 🔊 
+Calling all Freelance Creative &amp; Integrated Campaign talents! 
+We're looking for professionals with deep Indian market experience to help bring a global brand platform to life through a culturally authentic celebrity campaign. A strong understanding of Indian consumer behaviour, culture, and the media landscape is essential to create work that truly resonates with audiences.
+🔹 Business Director
+* 8+ years' integrated agency experience
+* Strong client leadership, project governance, and campaign delivery
+* Experience across large-scale integrated campaigns
+* Hospitality, travel, FMCG, or lifestyle experience is a plus
+🔹 Senior Art Director
+* 8–10+ years' integrated agency experience
+* Strong conceptual thinker with an outstanding campaign portfolio
+* Experience leading large productions and integrated campaigns
+* Celebrity campaign experience highly desirable
+🔹 Senior Copywriter
+* 6–8+ years' integrated agency experience
+* Exceptional conceptual and storytelling skills
+* Experience developing integrated campaigns across film, digital, and social
+* Hospitality, travel, or lifestyle experience preferred
+🔹 Project Manager
+* 5–8+ years' agency experience
+* Proven track record delivering integrated campaigns from planning through production
+* Strong production, stakeholder, and project management skills
+* Experience PM platforms is an advantage
+If you're passionate about creating culturally relevant, award-worthy work and thrive in a collaborative agency environment, we'd love to hear from you.
+📩 Please send your CV and portfolio (where applicable) to sean.genon@creategroup.me or feel free to tag or recommend someone who would be a great fit.
+#Hiring #Dubai #Advertising #CreativeJobs #AccountDirector #ArtDirector #Copywriter #IntegratedProducer #AgencyLife #Marketing #Campaigns</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-10 06:48:22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Muzammil Abedin</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/muzammilabedin01?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAAFw8_xABJOtVJjp78m0_0sODB5Soxsddvvg</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/muzammilabedin01_hiring-businessdevelopment-b2bsales-activity-7481207669404475392-dyN0?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>🚀 Hiring | Business Development Executive (B2B Sales)
+📍 Location: Barsha Heights, Dubai, UAE
+💰 Salary: AED 8,000/month + Incentives &amp; Other Benefits
+Are you passionate about building relationships, winning new business, and driving growth?
+We're looking for an experienced Business Development Executive to join our team in the UAE. This opportunity is ideal for professionals with a strong background in marketing and creative agency sales who thrive in a target-driven environment and enjoy working with corporate clients.
+Responsibilities: 
+• Identify and develop new business opportunities across the UAE
+• Build strong relationships with corporate clients and key decision-makers
+• Present and sell services including Branding, PR, Digital Marketing, Social Media Management, Website Development, Content Creation, Influencer Marketing, Events, and Business Consultancy
+• Prepare proposals, negotiate commercial terms, and successfully close deals
+• Consistently achieve sales targets while contributing to business growth
+What We're Looking For:
+✔ 3–5 years of UAE experience in Business Development within a Marketing, Branding, PR, Advertising, Media, or Digital Marketing Agency
+✔ Proven success in selling agency services to B2B clients
+✔ Excellent communication, presentation, and negotiation skills
+✔ Existing UAE corporate network is an advantage
+✔ UAE driving licence and own vehicle are preferred
+✔ Arabic language skills are a plus
+📌 Important: This role is intended for candidates with prior experience in a Marketing, Branding, PR, Advertising, Media, or Digital Marketing Agency. Applicants from other sales industries may not be considered.
+If you're ready to take the next step in your career and contribute to a growing organization, we'd love to hear from you.
+📩 Interested candidates can send their updated resume to: muzammilabedin1@gmail.com
+#Hiring #BusinessDevelopment #B2BSales #SalesJobs #MarketingAgency #DigitalMarketing #Branding #Advertising #PublicRelations #Media #UAEJobs #DubaiJobs #CareerOpportunity #NowHiring #Recruitment #BusinessGrowth #GulfJobs #UAECareers</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-09 19:33:05</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Bilal Ibrahim 🧲</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/bilal-ibrahim-dubai?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAAAqY9NUBsBo-zgbZfs0d5_Pr61PEiJTZcYg</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/bilal-ibrahim-dubai_13-years-ago-today-i-landed-in-dubai-i-activity-7481037726817927170-Grg1?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>13 years ago today, I landed in Dubai.
+I wasn’t a founder.
+I wasn’t an agency owner.
+I was just a guy from India, working the graveyard shift, hoping for a better future.
+Over the last 13 years, I’ve had the opportunity to work with incredible brands, including Emirates NBD and Danube.
+I’ve also built a business.
+Lost a business.
+Started again.
+Failed more than once.
+Won more than I expected.
+The biggest lesson Dubai taught me?
+This city doesn’t reward where you come from.
+It rewards the value you create.
+Nobody owes you success here.
+You earn it.
+One client.
+One relationship.
+One opportunity at a time.
+Looking back, I’m grateful for every challenge, every setback, and every person who believed in me.
+They shaped who I am today.
+So today, I just want to say…
+Thank you, Dubai.
+You changed the course of my life.
+And if someone who started with night shifts and a lot of uncertainty can build a life here…
+So can you.
+Bilal Ibrahim
+Lead That Convert
+12+ years in marketing.
+30+ businesses helped.
+$100M+ generated for clients.
+Qualified leads.
+Clean systems.
+Real conversions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-09 17:24:15</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Mariam Awad</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mariam-awad10?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAACG2QxUBfqO5xE4ADzUlkZTEhvxi_K0D2ZI</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/mariam-awad10_hiring-marketingjobs-assistantmarketingmanager-activity-7481005308098637824-YXvE?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>🚀 We're Hiring | Assistant Marketing Manager – Domino's GCC
+📍 Location: Dubai, UAE
+As an Assistant Marketing Manager, you'll play a key role in planning and executing integrated marketing campaigns, managing social media and CRM communications, coordinating with creative agencies, supporting local store marketing initiatives, tracking budgets, and collaborating with cross-functional teams to ensure flawless campaign execution.
+We're looking for someone with:
+✔ 5–7 years of marketing experience within QSR, F&amp;B, Retail, E-commerce, Food Delivery, or Consumer Brands
+✔ Experience in campaign management, CRM, social media, and agency management
+✔ Strong project management and stakeholder coordination skills
+✔ Commercial mindset with a passion for delivering business results
+✔ Good understanding of GCC consumer behavior and market dynamics
+✔ Fluent Arabic (Mandatory)
+✔ Currently residing in the UAE (Mandatory)
+If you're ready to take the next step in your marketing career with one of the world's leading QSR brands, we'd love to hear from you.
+📩 Apply now and share your CV with us via DM to explore this opportunity, or share it with your network.
+#Hiring #MarketingJobs #AssistantMarketingManager #Dominos #GCCJobs #DubaiJobs #MarketingCareers #QSR #RetailMarketing #FoodDelivery #EmployerBranding #NowHiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-09 15:46:10</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Salu Sunil</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/salu-sunil-1165521b5?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAADIXryIBTN7a4BLuhcgMOSPwJRcMVttv4C4</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/salu-sunil-1165521b5_marketingagency-digitalmarketing-socialmediamanagement-activity-7480980622702997505-j1mM?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Calling all Marketing Experts: Let’s collaborate !
+Hi
+We are currently looking for a reliable and creative digital marketing agency or marketing company to support our brand's growth.
+We are seeking a partner who can:
+1. Create engaging and professional content
+2. Design graphics and marketing materials
+3. Plan and execute digital marketing campaigns
+4. Improve our online presence and brand visibility
+5. Support website updates and other related marketing activities, if required
+We are looking for a team with experience in the healthcare sector and a strong portfolio of successful campaigns.
+If your company provides these services, or if you have a recommendation, pleasen dm. We'd love to connect and discuss potential collaboration.
+#MarketingAgency #DigitalMarketing #SocialMediaManagement #Dubai #Branding #MarketingPartner</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-09 15:41:09</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Ashutosh Nanda</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ashutosh-nanda-b1a3771b0?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAADEtEIYB5bJoTuQ0GsE8MXU8O6TAgHdk_Js</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/ashutosh-nanda-b1a3771b0_dubai-digitalagency-webdevelopment-activity-7480979359269548032-JovV?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>I wasn’t planning to offer this publicly…
+Over the last few months, we’ve been building software and AI solutions for companies in Dubai.
+One of the projects was an AI Website Generator that can create a complete business website in minutes instead of weeks.
+That got me thinking…
+How many agencies are losing clients because they don’t have enough developers, designers, or AI engineers to keep up?
+So here’s my proposal.
+If you’re a marketing agency, branding agency, or design studio…
+You bring the client.
+We’ll build everything behind the scenes.
+✅ Websites
+✅ Custom Software
+✅ SaaS Platforms
+✅ AI Chatbots
+✅ AI Voice Agents
+✅ Business Automation
+✅ Internal Portals
+✅ CRM Systems
+Most projects start under $1,000.
+You decide what to charge your client.
+We never approach your client directly.
+Everything is white-label.
+We stay involved until your client is 100% happy.
+We’re looking for 5 agency partners to work with long-term—not hundreds.
+If you’ve ever turned down a project because you didn’t have the technical team to deliver it…
+Send me “PARTNER” in a DM.
+Let’s help each other grow.
+#Dubai #DigitalAgency #WebDevelopment #ArtificialIntelligence #SoftwareDevelopment #WhiteLabel #BusinessGrowth #AgencyLife #Automation #SaaS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-09 15:29:39</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Mahi Khan Khushik</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mahi-khan-khushik?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAAGPj0-gBC7nOCp_t1LEzri986fWTJmmuClE</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/mahi-khan-khushik_facebookadsspecialist-digitalmarketingmanager-activity-7480976466055442432-ztNC?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>If you own a dental clinic in Dubai or anywhere else, you probably know how frustrating it is to spend money on social media ads and only get fake leads, wrong phone numbers, or people who disappear after asking for prices.
+At the end of the day, your dental chairs stay empty and your marketing budget is gone.
+I am a Paid Ads Specialist and Media Buyer. My job is not just running random ads, but targeting real customers who live in your area and can actually afford high value treatments like Invisalign, implants, and veneers.
+Right now, I am looking for new remote jobs, monthly freelance projects, or contract work to manage and fix your ad accounts.
+I can take full control of your advertising campaigns so you do not have to worry about the technical setup, or I can train you and your clinic staff so you can run your own ads easily without paying monthly agency fees anymore.
+There are no confusing words or complicated reports here, just honest and direct execution to stop your budget from leaking.
+If you are looking for an independent digital marketer to bring real patients to your clinic, please send me a direct message right now and let us schedule a quick chat.
+#FacebookAdsSpecialist #DigitalMarketingManager #PerformanceMarketer #MediaBuyer #RemoteJobs #PaidAdsExpert #DentalMarketing #FreelanceMarketer #DubaiBusiness #LeadGeneration</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-09 14:55:01</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Tanishqa Kambli</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tanishqa-kambli?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAACqSXtkB0rZI-iSiYCXO6JVDymiBTUBC5ds</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/tanishqa-kambli_spjain-spjainglobal-studentstories-activity-7480967752711585792-rMj8?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>18: that's how old I was when I walking onto campus with hope and ambition, but no with idea how I was going to do it all.
+Looking at this feature today, it feels like a beautiful, full-circle moment.
+Thank you, SP Jain School of Global Management - Dubai, Mumbai, Singapore &amp; Sydney, for the spotlight and for reminding me where this entire spark started. 
+Launching the Marketing &amp; More club back then wasn’t just a student activity: it was my very first experiment in building an ecosystem from scratch.
+If university taught me anything, it’s that the professional world doesn't care about templates. It taught me how to think on my own feet, embrace the messy process of leadership, and realize that absolutely anything is possible if you just have the courage to be open and ask.
+That exact mindset is the reason why, a couple of months ago, I took the ultimate leap and founded MuseInc.ae.
+I didn't start Muse to build a traditional, rigid agency. The world has enough noise and artificial marketing fluff. I started Muse to re-engineer how brands think, marrying high-end creative storytelling (video, branding, audio) with automated backend systems that actually let a business breathe.
+We are based out of Dubai, but we are running around the world.
+We aren't bound by standard corporate formats, and we are certainly not bound by geography. We choose to be open, fluid, and completely free. 
+True creativity doesn't recognize borders, and that's what my experience at SP Jain helped me recognise: a borderless world, interconnected. 
+Whether you are a visionary founder looking to inject raw truth into your brand, a killer freelancer looking for a systemized collective to plug into, or an agency looking to sync forces: our doors are wide open. We are ready to collaborate across all industries, globally.
+Let’s connect, remove the boundaries, and see what we can build together. 🌐✨
+Drop a message or reach out directly at tan@museinc.ae. Let's create your muse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-09 14:29:33</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Alireza Moeini</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alirezamoeinizoom?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAAAXc10QBQXGIQMGwMO8Tw3KObAV7QyrXTiM</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/alirezamoeinizoom_dubailuxuryhomes-dubairealestate-luxuryvillasdubai-activity-7480961342133350400-Gyn5?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>🎬 Cinematic Visuals that Sell: Luxury Real Estate &amp; Brand Storytelling in Dubai
+With over 22 years of hands-on experience behind the lens, I specialize in transforming premium spaces and brand narratives into high-impact visual assets. As a Dubai-based Video Producer and Professional Photographer, my core expertise lies in luxury property video production and elite real estate photography—delivering cinematic property showcases and digital campaigns that capture attention and drive tangible business results.
+In Dubai's fast-paced market, I understand that timing and quality are everything. I bridge the gap between rapid turnaround and top-tier production value, combining technical precision with creative storytelling. From directing high-end architectural shoots to crafting engaging visual narratives for prominent brands, my focus remains on elevated aesthetics and absolute professionalism.
+Whether you are a luxury real estate developer, a premium agency, or a brand looking to dominate your digital space, I bring your vision to life with visuals that resonate.
+🏆 Core Expertise:
+Luxury Real Estate &amp; Architectural Video Production
+Professional Property &amp; Commercial Photography
+High-End Digital Marketing Campaigns
+End-to-End Creative Direction &amp; Fast-Turnaround Post-Production
+🔗 Explore my portfolio &amp; cinematic work: https://lnkd.in/dNisz7tk 📞 Let’s collaborate: +971 52 551 5387 | Dubai, UAE
+#DubaiLuxuryHomes #DubaiRealEstate #LuxuryVillasDubai #DubaiProperty #EmaarBeachfront #LuxuryLivingDubai #DubaiMansions #PremiumRealEstate</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-14 13:58:08</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Hilal Abu Askar</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/h-abuaskar?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAABiyf6gBWS2soBdwKczMy7ZANLtKNikjbHM</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/h-abuaskar_%D9%88%D8%B8%D8%A7%D8%A6%D9%81-%D8%B9%D8%A7%D9%85%D8%A9-%D9%85%D8%B7%D9%84%D9%88%D8%A8-%D9%84%D8%B4%D8%B1%D9%83%D8%A9-%D9%81%D9%8A-%D9%84%D9%84%D8%B9%D9%85%D9%84%D9%81%D9%8A-%D8%B9%D8%AF%D8%A9-%D9%85%D8%B4%D8%A7%D8%B1%D9%8A%D8%B9-activity-7471893741104971776-K2fb?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>وظائف عامة
+مطلوب لشركة في للعمل في عدة مشاريع بالمملكة 
+- مهندس مدني 
+- مهندس مرور وسلامة 
+- مراقب سلامة 
+- حاسب كميات ( طرق )
+المتطلبات 
+- خبرة ثلاث سنوات فأعلى 
+- سعودي الجنسية 
+- خبرة قي مجال الطرق والبنية التحتية 
+الرجاء ارسال السيرة الذاتية للأيميل التالي 
+Abdulmajiidhr@gmail.com
+إعلان وظيفي: أخصائي تسويق 📢
+تعلن شركة أوبرا للأزياء بمدينة الرياض عن رغبتها في استقطاب موهبة وطنية للانضمام إلى فريقنا الإبداعي.
+المسؤوليات الرئيسية:
+• إدارة حسابات التواصل الاجتماعي بفعالية.
+• كتابة نصوص إعلانية (Copywriting) جذابة.
+• المساعدة في تنسيق جلسات التصوير والمحتوى.
+• متابعة الموردين والمطابع والجهات الخارجية.
+• التفاعل مع استفسارات العملاء عبر المنصات الرقمية.
+الشروط والمتطلبات:
+• شهادة جامعية في مجال ذو صلة.
+• خبرة عملية (سنة كحد أدنى).
+• ذائقة فنية عالية واهتمام بمجال الأزياء والموضة.
+• مهارات تواصل ممتازة والعمل بروح الفريق.
+• إجادة استخدام تطبيقات الجوال لإنتاج المحتوى السريع.
+المزايا:
+• بيئة عمل محفزة وحيوية.
+• خصومات خاصة للموظفين.
+• فرص حقيقية للتطور المهني.
+للتقديم:
+يرجى إرسال السيرة الذاتية (ويُفضل إرفاق نماذج الأعمال) إلى البريد الإلكتروني:
+📧 jobs@opera-sa.com
+(يرجى ذكر المسمى الوظيفي في عنوان الرسالة)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-06-13 20:15:05</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Mahmoud Abd Elfattah</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mahmoud-abd-elfattah-404760290?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAAEaXPEQBElRuO83YSTHpBj3VmTdFsMzs3cM</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/mahmoud-abd-elfattah-404760290_aecaeyaezabraepaeyabraepaesaewaeyaez-activity-7471626215368622080-ZV02?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>مطلوب مندوبي مبيعات للعمل في الرياض
+تعلن شركة آفاق التعاون للتجارة عن حاجتها لتوظيف مندوبي مبيعات للعمل بمدينة الرياض.
+المسمى الوظيفي:
+مندوب مبيعات
+مكان العمل:
+الرياض
+طبيعة العمل:
+- العمل بنظام 8 ساعات يوميًا.
+- تسويق وبيع منتجات أخشاب البناء (Plywood).
+- استقطاب عملاء جدد وتطوير العلاقات مع العملاء الحاليين.
+- تحقيق أهداف المبيعات المحددة.
+- متابعة السوق والمشاريع والعملاء المحتملين.
+الشروط والمتطلبات:
+- خبرة لا تقل عن سنتين في مجال مبيعات الأخشاب، ويفضل في منتجات Plywood.
+- توفر قاعدة بيانات وعلاقات قوية مع المقاولين وشركات البناء ومؤسسات مواد البناء.
+- القدرة على تحقيق مبيعات وإغلاق صفقات من الأسبوع الأول للعمل.
+- مهارات تواصل وتفاوض وإقناع ممتازة.
+- رخصة قيادة سارية المفعول.
+- الجدية والالتزام وتحمل ضغط العمل.
+المميزات:
+- راتب مجزٍ يحدد بعد المقابلة.
+- عمولات وحوافز على المبيعات.
+- بيئة عمل محفزة وفرص للتطوير.
+للتقديم وإرسال السيرة الذاتية عبر واتساب:
+0596895195
+0597771191
+#شير_في_الخير</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-12 20:09:10</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Hilal Abu Askar</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/h-abuaskar?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAABiyf6gBWS2soBdwKczMy7ZANLtKNikjbHM</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/h-abuaskar_%D9%88%D8%B8%D8%A7%D8%A6%D9%81%D8%B4%D8%A7%D8%BA%D8%B1%D8%A9-%D9%85%D8%B7%D9%84%D9%88%D8%A8-%D9%85%D9%88%D8%B8%D9%81%D9%80-%D9%80%D8%A9-%D8%A7%D8%AE%D8%B5%D8%A7%D8%A6%D9%8A-%D8%AA%D8%B3%D9%88%D9%8A%D9%82-activity-7471262338352984064-81Yq?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>وظائف_شاغرة 
+ مطلوب  موظفـ /ـة اخصائي تسويق وإدارة وسائل التواصل الاجتماعي للانضمام إلى فريق العمل في شركة شرق الرياض 
+المتطلبات:
+•خبرة عملية في إدارة حسابات السوشيال ميديا تتراوح بين  ١ إلى ٣ سنوات.
+•تخصص  في مجال التسويق أو الإعلام. 
+•القدرة على إعداد وتنفيذ خطط المحتوى.
+•مهارات تحليل الأداء والتقارير.
+•الإبداع في صناعة المحتوى والتفاعل مع الجمهور.
+•إجادة استخدام الأدوات والمنصات ذات الصلة.
+للتقديم، يرجى إرسال السيرة الذاتية إلى
+mak.co.hr55@gmail.com 
+ويكون عنوان الإيميل هو المسمى الوظيفي
+ We’re Hiring: Commercial Contracts specialist
+Al-Masaq Group for Support Services is looking for a dynamic and result-oriented Commercial Contracts Manager to join our team in Riyadh. This role is designed for a professional who can expertly manage our contract lifecycle while actively driving business growth by securing new contracts and commercial opportunities.
+Role Overview:
+You will bridge the gap between risk management and business expansion. Your mission is twofold: ensuring our current agreements are airtight and legally sound, while proactively hunting for and securing new commercial contracts to expand our market footprint.
+Key Responsibilities:
+•	Contract Management: Draft, review, and negotiate various commercial contracts and service agreements, ensuring full legal and financial protection for the company.
+•	Business Development: Actively identify, pursue, and secure new contract opportunities and client accounts to drive revenue.
+•	Risk &amp; Compliance: Evaluate risks in potential agreements and provide strategic recommendations to senior management.
+•	Relationship Management: Build and maintain strong, long-term relationships with new and existing clients, partners, and vendors.
+Qualifications &amp; Requirements:
+•	Experience: Minimum of 3 years of proven experience in commercial contracts, business development, or a combined role.
+•	Language: Full professional fluency in English (both written and spoken) is mandatory.
+•	Education: Bachelor’s degree in business administration, Law, Marketing, or a related field.
+•	Strong commercial acumen with a proven track record in negotiation and closing deals.
+•	Result-driven with excellent communication and relationship-building skills.
+What We Offer:
+•	Highly competitive and attractive salary package (Fixed package based on experience and qualifications).
+•	Comprehensive medical 
+insurance.
+•	📩 How to Apply:
+•	Please send your updated CV directly to our HR email with "Commercial Contracts Manager" in the subject line: 
+H.Khaytan@almassaq.com
+Riyadh</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:50:07</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SAUD ALQAHTANI MBA,SHRM-ACHRM,C-KPI’S</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/saud-alqahtani-shrm?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAABJPpTkBnJrqSabVJa9a7xULyfQfLsENAaE</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/saud-alqahtani-shrm_%D9%85%D8%B7%D9%84%D9%88%D8%A8-%D9%85%D9%88%D8%B8%D9%81%D9%80-%D9%80%D8%A9-%D8%A7%D8%AE%D8%B5%D8%A7%D8%A6%D9%8A-%D8%AA%D8%B3%D9%88%D9%8A%D9%82-%D9%88%D8%A5%D8%AF%D8%A7%D8%B1%D8%A9-%D9%88%D8%B3%D8%A7%D8%A6%D9%84-activity-7471000851864670208-8iZt?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>مطلوب  موظفـ /ـة اخصائي تسويق وإدارة وسائل التواصل الاجتماعي للانضمام إلى فريق العمل في شركة شرق الرياض 
+المتطلبات:
+•خبرة عملية في إدارة حسابات السوشيال ميديا تتراوح بين  ١ إلى ٣ سنوات.
+•تخصص  في مجال التسويق أو الإعلام. 
+•القدرة على إعداد وتنفيذ خطط المحتوى.
+•مهارات تحليل الأداء والتقارير.
+•الإبداع في صناعة المحتوى والتفاعل مع الجمهور.
+•إجادة استخدام الأدوات والمنصات ذات الصلة.
+للتقديم، يرجى إرسال السيرة الذاتية إلى
+mak.co.hr55@gmail.com 
+ويكون عنوان الإيميل هو المسمى الوظيفي
+منقول</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:59:34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Mahmoud Abd Elfattah</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mahmoud-abd-elfattah-404760290?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAAEaXPEQBElRuO83YSTHpBj3VmTdFsMzs3cM</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/mahmoud-abd-elfattah-404760290_aecaeyaezabraepaeyabraepaesaewaeyaez-activity-7470973030693871616-vqBW?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>مطلوب مندوب مبيعات للعمل لدى شركة متخصصة في المصاعد بمدينة الرياض.
+الشروط:
+خبرة سابقة في تسويق وبيع المصاعد.
+وجود رخصة قيادة سارية.
+يشترط الخبرة، ولن يتم النظر في الطلبات غير المطابقة.
+المميزات:
+راتب أساسي مناسب.
+عمولات مجزية وفورية.
+مكان العمل: الرياض.
+للتواصل وإرسال السيرة الذاتية: واتساب فقط 0569016194
+#شير_في_الخير</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-06-11 12:11:23</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Fatimah Al RIBHI</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fatimah-al-ribhi-05266013a?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAACHpjj4BYZbLsJLADXSUeRbGTUCHmZGTdVI</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/fatimah-al-ribhi-05266013a_%D8%A7%D8%B9%D9%84%D8%A7%D9%86-%D9%88%D8%B8%D9%8A%D9%81%D9%8A-%D9%85%D8%B7%D9%84%D9%88%D8%A8-%D9%85%D9%88%D8%B8%D9%81%D9%80-%D9%80%D8%A9-%D8%A7%D8%AE%D8%B5%D8%A7%D8%A6%D9%8A-%D8%AA%D8%B3%D9%88%D9%8A%D9%82-activity-7470779712810897408-wVlD?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>اعلان وظيفي:
+مطلوب  موظفـ /ـة اخصائي تسويق وإدارة وسائل التواصل الاجتماعي للانضمام إلى فريق العمل في شركة شرق الرياض 
+المتطلبات:
+•خبرة عملية في إدارة حسابات السوشيال ميديا تتراوح بين  ١ إلى ٣ سنوات.
+•تخصص  في مجال التسويق أو الإعلام. 
+•القدرة على إعداد وتنفيذ خطط المحتوى.
+•مهارات تحليل الأداء والتقارير.
+•الإبداع في صناعة المحتوى والتفاعل مع الجمهور.
+•إجادة استخدام الأدوات والمنصات ذات الصلة.
+للتقديم، يرجى إرسال السيرة الذاتية إلى
+mak.co.hr55@gmail.com 
+ويكون عنوان الإيميل هو المسمى الوظيفي</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-06-10 10:45:56</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Mohamed Selim</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mohamed-selim-ba30b83a0?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAAGJCN6sBgmCKFwYbO3xxzu1nUQkKlnNM0LM</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/mohamed-selim-ba30b83a0_%D9%85%D8%B7%D9%84%D9%88%D8%A8-%D9%85%D9%87%D9%86%D8%AF%D8%B3-%D9%85%D8%A8%D9%8A%D8%B9%D8%A7%D8%AA-%D8%AA%D8%B9%D9%84%D9%86-%D8%B4%D8%B1%D9%83%D8%A9-%D9%85%D8%AA%D8%AE%D8%B5%D8%B5%D8%A9-%D9%81%D9%8A-activity-7470395820794695680-K1Ph?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>📢 مطلوب مهندس مبيعات
+تعلن شركة متخصصة في اختبارات التربة والخرسانة ومواد البناء بمدينة الرياض – المملكة العربية السعودية عن حاجتها إلى:
+مهندس مبيعات (Sales Engineer)
+المهام الوظيفية:
+تسويق خدمات الشركة الخاصة باختبارات التربة والخرسانة ومواد البناء.
+استقطاب العملاء الجدد وبناء علاقات مهنية طويلة الأمد.
+إعداد العروض الفنية والمالية ومتابعة العملاء.
+تحقيق المستهدفات البيعية الشهرية والسنوية.
+التنسيق مع الإدارات الفنية لضمان تقديم أفضل خدمة للعملاء.
+متابعة المشاريع والمناقصات ذات العلاقة بمجال عمل الشركة.
+المتطلبات:
+بكالوريوس هندسة مدنية أو تخصص ذو صلة.
+خبرة في المبيعات الهندسية أو في مجال المختبرات واختبارات مواد البناء.
+مهارات عالية في التواصل والتفاوض وإعداد العروض الفنية.
+القدرة على تحقيق الأهداف البيعية والعمل تحت الضغط.
+إجادة استخدام برامج الحاسب الآلي وMicrosoft Office.
+يفضل وجود رخصة قيادة سارية.
+للتقديم:
+📧 البريد الإلكتروني: info.ram1006@gmail.com
+📱 واتساب: +966598921480</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-06-10 06:01:43</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Mahmoud Abd Elfattah</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mahmoud-abd-elfattah-404760290?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAAEaXPEQBElRuO83YSTHpBj3VmTdFsMzs3cM</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/mahmoud-abd-elfattah-404760290_aecaeyaezabraepaeyabraepaesaewaeyaez-activity-7470324294812688384-PVsI?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>مطلوب أخصائي تسويق ومبيعات (Marketing Specialist) – الرياض
+تعلن شركة متخصصة في مجال الزي الموحد (Uniforms) عن رغبتها في استقطاب أخصائي تسويق ومبيعات للانضمام إلى فريق العمل بمدينة الرياض.
+المتطلبات:
+- العمر لا يتجاوز 34 سنة.
+- إجادة اللغة الإنجليزية بمستوى ممتاز تحدثاً وكتابة.
+- خبرة سابقة في مجال التسويق والمبيعات.
+- خبرة في قطاع الزي الموحد (Uniforms) والشركات.
+- مهارات قوية في التواصل وبناء العلاقات مع العملاء.
+- القدرة على تحقيق المستهدفات البيعية وتطوير الأعمال.
+- تأشيرة من مصر أو نقل كفالة.
+المهام الوظيفية:
+- البحث عن عملاء جدد وتطوير قاعدة العملاء.
+- تسويق منتجات الشركة وعروضها للشركات والمؤسسات.
+- إعداد العروض التجارية ومتابعة العملاء المحتملين.
+- تحقيق المستهدفات البيعية الشهرية.
+- بناء علاقات طويلة الأمد.
+المزايا:
+- راتب مجزٍ.
+- عمولات ونسب مبيعات محفزة.
+- سيارة عمل.
+- فرص للتطور الوظيفي والنمو المهني.
+- بيئة عمل احترافية.
+للمهتمين، يرجى إرسال السيرة الذاتية مع ذكر المسمى الوظيفي في عنوان الرسالة.
+للتواصل:
++966550615496
+Hr Amr
+#شير_في_الخير</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-06-14 13:55:21</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Mohamed Nader</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mohamed-nader-4b6961211?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAADW2a4oBjKE9qr4MM4EHPp9FWD3MXkkXCGc</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/mohamed-nader-4b6961211_%D9%81%D9%8A-%D8%A7%D8%AA%D8%AC%D8%A7%D9%87-%D8%AC%D8%AF%D9%8A%D8%AF-%D9%81%D9%8A-%D8%A7%D9%84%D8%AA%D8%B5%D9%85%D9%8A%D9%85-%D8%A7%D9%84%D8%AF%D8%A7%D8%AE%D9%84%D9%8A-%D9%81%D9%8A-2026-activity-7471893040136245248-ZtRa?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>في اتجاه جديد في  التصميم الداخلي في 2026... وكتير مصممين لسه مش واخدينه بجدية
+استطلاع شارك فيه 468 مصمم داخلي من كل أنحاء العالم كشف حاجة مهمة:
+عصر الـ Minimalism والحيطان البيضاء الفاضية... خلص.
+اللي بيسيطر دلوقتي هو الـ "Thoughtful Maximalism" — يعني مساحات دافية، متعددة الطبقات، وبتحكي هوية صاحبها، مش بس بتمشي مع الترند.
+أبرز اللي شايفينه في 2026:
+خشب غامق بنسيج طبيعي واضح (Burl &amp; Reeded Wood)
+البني الغامق كأكتر لون مطلوب — اختاره أكتر من 30% من المصممين
+خامات طبيعية تاكتيلية: بلاط يدوي، كتان، حجر خام
+الإضاءة المحيطية كعنصر تصميمي بالدرجة الأولى.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-06-12 09:21:32</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Jobayti</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jobayti/posts</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/jobayti_jobayti-freelance-aewaegaepaeoaep-activity-7471099355756761088-1qNh?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>🚀 فرصة جديدة على منصة مستقل
+📌 العنوان: مطلوب مصمم هوية بصرية محترف لكوفي شوب ، براندنج متكامل، وتصميم باكيجينج ومواد تسويقية)
+📋 التفاصيل: نبحث عن مصمم هوية بصرية ومطور علامات تجارية محترف ومبدع، يمتلك مهارة استثنائية وخبرة مثبتة في بناء الهويات التجارية في Behance او باقي برامج التصميم، وتحديدا في قطاع المطاعم والكافيهات. نحن نبحث عن مصمم مبدع و قادر على ابتكار روح كاملة للمشروع، وصناعة تفاصيل تميزنا في السوق. المهام والمخرجات المطلوبة: 1 تطوير الاسم والشعار (Naming Logo): المساعدة في استعراض واختيار أسماء رنانة ومبتكرة للمطعم (إذا تطلب الأمر). تصميم شعار (Logo) فريد، مبتكر، ويعكس ...
+🔗 قدّم الآن: https://lnkd.in/defmAZfY
+---
+للمزيد من الفرص، زور موقعنا الإلكتروني:
+🔗 https://jobayti.live/
+وإذا عملت حساب مجاني على Jobayti، هتظهر لك الوظائف حسب تخصصك ومهاراتك اللي اخترتها في صفحة الوظائف المخصصة.
+#Jobayti #freelance #وظائف #وظيفة_اليوم</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-06-10 18:41:58</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Jobayti</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jobayti/posts</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/jobayti_jobayti-freelance-aewaegaepaeoaep-activity-7470515616781844480-M9XR?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsBj-cBEhYTqGMIP4ZhDmlfgumMcHM-GVk</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>🚀 فرصة جديدة على منصة مستقل
+📌 العنوان: تصميم عدد 12 بوست سوشيال ميديا
+📋 التفاصيل: مطلوب مصمم/ة بوستات سوشيال ميديا بشكل احترافي وعصري المطلوب: تصميم عدد 12 بوست سوشيال ميديا بأسلوب إبداعي وجذاب يتماشى مع هوية المشروع. المهام: تصميم بوستات ثابتة (صور/كاروسيل حسب الحاجة). الالتزام بالهوية البصرية والتعليمات التسويقية. تسليم التصاميم بصيغ جاهزة للنشر الملفات المفتوحة. القدرة على التعديل السريع حسب الملاحظات. الشروط: خبرة سابقة في تصميم محتوى السوشيال ميديا. إتقان برامج التصميم (Photoshop / Illustrator / Canva أو غيرها). حس إبداعي...
+🔗 قدّم الآن: https://lnkd.in/dtansewb
+---
+للمزيد من الفرص، زور موقعنا الإلكتروني:
+🔗 https://jobayti.live/
+وإذا عملت حساب مجاني على Jobayti، هتظهر لك الوظائف حسب تخصصك ومهاراتك اللي اخترتها في صفحة الوظائف المخصصة.
+#Jobayti #freelance #وظائف #وظيفة_اليوم</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-08 09:52:28</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>The Design &amp; Style Studio FZ-LLC</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/thedesignstylestudio/posts</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/thedesignstylestudio_exhibitiondesign-boothdesign-tradeshow-activity-7480529222311178240-ge3u?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsABCwBsx4fHkp61BwbvkLPvpYju73n3x4</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Crafted Spaces. Unforgettable Presence. ✨
+Your exhibition stand is more than a booth—it's your brand's first impression. At Design and Style Studio, we design, fabricate, and deliver premium exhibition stands that combine innovative architecture, flawless craftsmanship, and impactful branding to help your business stand out on the show floor.
+From concept development and 3D visualization to fabrication, installation, and turnkey execution, we create exhibition experiences that captivate visitors, generate quality leads, and elevate your brand presence across the UAE and beyond.
+Ready to make your next exhibition unforgettable? Let's build something extraordinary.
+#ExhibitionDesign #BoothDesign #TradeShow #BrandExperience #DubaiBusiness
+( Custom Exhibition Booth, Exhibition Stand Builder UAE, Trade Show Booth Design, Booth Fabrication Dubai, Exhibition Company UAE, Event Branding Solutions, Turnkey Exhibition Solutions, Exhibition Stall Design, Premium Booth Design, Exhibition Stand Contractor, Interior Branding )</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-06 11:20:13</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>The Builder UAE</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/the-builder-uae/posts</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/the-builder-uae_fitoutsolutions-interiorsolutions-customcarpentry-activity-7479826529225478144-dQRY?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsABCwBsx4fHkp61BwbvkLPvpYju73n3x4</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>We build more than spaces. We deliver solutions that support how people work, move, connect, and experience their environment.
+With a complete range of services covering fit-out works, interior solutions, custom carpentry, traffic and parking systems, exhibition booths, digital displays, facility management, and building maintenance, we bring every project from concept to execution with precision and reliability.
+Our focus is simple: practical solutions, professional execution, and spaces made to perform.
+نحن لا ننفذ المساحات فقط، بل نقدم حلولاً متكاملة تدعم طريقة العمل والحركة والتواصل داخل كل بيئة.
+من أعمال التشطيبات والتصميم الداخلي والنجارة المخصصة، إلى حلول المرور والمواقف، وأجنحة المعارض، والشاشات العرض، وإدارة المرافق، وصيانة المباني، نعمل على تحويل كل مشروع من الفكرة إلى التنفيذ باحترافية ودقة.
+هدفنا واضح: حلول عملية، تنفيذ احترافي، ومساحات مصممة للأداء والاستمرارية.
+#FitOutSolutions #InteriorSolutions #CustomCarpentry #TrafficSolutions #ParkingSolutions #ExhibitionBooths #DigitalDisplaySolutions #FacilityManagement #BuildingMaintenance #TurnkeySolutions #ProjectExecution #UAEProjects</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-03 10:21:08</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Rahul Wadhwa</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/iamrahulwadhwa?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAAAjcTcoBSe87icTR0a7LSnnHy3V6tS2wGxo</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/iamrahulwadhwa_where-the-travel-tech-industry-connects-activity-7478724499530584064-MUsy?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsABCwBsx4fHkp61BwbvkLPvpYju73n3x4</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>🌍 Arabian Travel Market (ATM) 2026 is one of the Middle East's most influential travel and tourism exhibitions, bringing together thousands of tourism boards, destinations, hospitality brands, airlines, travel technology companies, and industry professionals from around the world.
+If you're planning to exhibit, remember: Your booth is your brand's first impression.
+In a highly competitive exhibition hall, simply being present isn't enough. Your stand should attract visitors, encourage meaningful conversations, and create memorable brand experiences that lead to real business opportunities.
+At Skyline Events- The Expo Builders (A Unit of Build-Craftxpo International Pvt. Ltd.), we help exhibitors stand out with:
+ ✅ Creative custom booth designs that attract more visitors
+ ✅ Premium fabrication with flawless execution
+ ✅ Interactive brand experiences that increase engagement
+ ✅ Complete turnkey solutions -from design to dismantling
+ ✅ Dedicated on-site project management for a hassle-free experience
+With execution capabilities across the UAE, Saudi Arabia, Europe, India, and beyond, we ensure your exhibition presence reflects the quality of your brand.
+Planning to exhibit at Arabian Travel Market 2026?
+Let's build a stand that not only turns heads but also delivers measurable business results.
+📩 Get in touch:
+ 📧 marketing@skylineevents.services
+ 🌐 www.skylineevents.co.in
+Design. Build. Deliver. Results.
+#ArabianTravelMarket #ATM2026 #ArabianTravelMarket2026 #ExhibitionDesign #ExhibitionBooth #TradeShow #TravelIndustry #Hospitality #Dubai #ExpoBuilders #SkylineEvents #EventMarketing #ExperientialMarketing #BoothDesign #BusinessGrowth #UAE #Tourism #MICE #TradeShows</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-06-30 08:25:26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Expo Worldwide Ltd</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/expo-worldwide/posts</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/expo-worldwide_expoworldwide-exhibitionstand-boothdesign-activity-7477608217318121473-BmiW?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsABCwBsx4fHkp61BwbvkLPvpYju73n3x4</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>𝐒𝐦𝐚𝐥𝐥 𝐁𝐨𝐨𝐭𝐡 𝐨𝐫 𝐋𝐚𝐫𝐠𝐞 𝐁𝐨𝐨𝐭𝐡? 𝐖𝐡𝐢𝐜𝐡 𝐎𝐧𝐞 𝐖𝐢𝐧𝐬? 🤔
+The answer isn't about size it's about 𝐬𝐭𝐫𝐚𝐭𝐞𝐠𝐲.
+A small booth can generate outstanding ROI with the right layout, messaging, and visitor flow. A large booth offers greater visibility and brand presence when designed with purpose.
+At 𝐄𝐱𝐩𝐨 𝐖𝐨𝐫𝐥𝐝𝐰𝐢𝐝𝐞, we create exhibition stands that maximize impactwhether your space is compact or expansive.
+Because in exhibitions, 𝐬𝐦𝐚𝐫𝐭 𝐬𝐭𝐫𝐚𝐭𝐞𝐠𝐲 𝐚𝐥𝐰𝐚𝐲𝐬 𝐛𝐞𝐚𝐭𝐬 𝐬𝐢𝐳𝐞.
+🌍 Asia | Europe | UAE | USA
+📞 +36 20 541 4370 | +91 93501 16878
+🌐 www.expoworldwides.com
+Large Booth Design | Trade Show Booth | Custom Exhibition Stand | Booth Fabrication | Exhibition Services | Event Solutions | Brand Experience | Global Exhibition Company | Exhibition Contractor | Trade Show Design | Exhibition Stand Builder | Booth Strategy | Exhibition Marketing | Exhibition Display | Modular Booth | Custom Booth Design
+#expoworldwide #exhibitionstand #boothdesign #smallbooth #largebooth #tradeshow #exhibitiondesign #custombooth #boothfabrication #eventmarketing #brandexperience #leadgeneration #tradeshowbooth #exhibitionservices</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-06-29 08:34:28</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Trio Creations</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/triocreation/posts</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/triocreation_triocreation-exhibitionstand-boothdesign-activity-7477248105310998528-9Zjk?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsABCwBsx4fHkp61BwbvkLPvpYju73n3x4</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Exhibition Booth Design UAE | Custom Exhibition Stand Builder Dubai
+Your exhibition stand is more than a structure—it's your brand's first impression.
+From custom booth design and fabrication to turnkey exhibition solutions, Trio Creations delivers stunning exhibition spaces that attract visitors and generate business.
+✅ Custom Stall Design
+✅ Turnkey Execution
+✅ LED &amp; Display Solutions
+✅ On-Time Delivery
+📞 +971 508439699
+📧 info@triocreations.ae
+🌐 https://lnkd.in/g6eDKs5N
+#triocreation #exhibitionstand #boothdesign #dubaibusiness #exhibitiondesign #tradeshow #custombooth #eventsuae #expodubai #triocreations #brandexperience</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-06-24 11:50:50</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Vaishnavi Agrahari</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vaishnavi-agrahari?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAADn1pO8Biec_ZYpshhuAi5eQ-iVrZtaLwVw</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/vaishnavi-agrahari_team-skyline-events-the-expo-builders-a-activity-7475485583579185152-gGgB?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsABCwBsx4fHkp61BwbvkLPvpYju73n3x4</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Team Skyline Events- The Expo Builders (A Unit of Build-Craftxpo International Pvt. Ltd.) is Proud to have worked with Rahul Agro Industries at Prod Expo 2026, Crocus Expo Center, Moscow 🇷🇺
+Taking an Indian brand to a global platform is always special. From design to on-site execution, our team ensured a clean, impactful booth that reflected Rahul Agro’s quality and attracted strong visitor engagement throughout the show.
+International projects come with challenges tight timelines, logistics, and coordination across borders but with the right partnership and teamwork, everything comes together seamlessly. Grateful for the trust and collaboration.
+Planning to exhibit in India, UAE, Europe, Russia, or Southeast Asia? Let’s connect and build your next exhibition success.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-06-24 10:02:23</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>HK Communication PVT.LTD.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/hk-communication-pvt-ltd/posts</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/hk-communication-pvt-ltd_cphi2026-cphimilan-exhibitiondesign-activity-7475458288738897920-5wDs?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsABCwBsx4fHkp61BwbvkLPvpYju73n3x4</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>🌍 Exhibiting at CPHI Milan 2026?
+Make your brand impossible to ignore with a custom-designed exhibition stand that attracts visitors, creates engagement, and delivers results.
+At HK Communication Pvt. Ltd., we specialize in premium exhibition stall design, fabrication, and turnkey execution for international trade shows. From concept to completion, our team ensures your brand stands out on the global stage.
+   📍 CPHI Milan 2026
+ 📅 6–8 October 2026
+ 🏛️ Fiera Milano, Italy
+Whether you need a bespoke stand, country pavilion, product showcase, or experiential brand space, we've got you covered.
+Let's create an exhibition experience that drives conversations, connections, and business opportunities.
+ Contact us - +91 99581 91313 | +971-529923448
+🌐 www.hkcomunication.com
+(Exhibition Stand Design Italy, Exhibition Booth Contractor Germany, Trade Show Booth Dubai, Exhibition Company UAE, Stall Fabrication Thailand, Custom Booth Builder Europe, Exhibition Design Company Italy, International Exhibition Services, Turnkey Exhibition Solutions, Brand Experience Agency Europe, Exhibition Marketing Company Dubai, Pharma Exhibition Booth Design, CPHI Milan Booth Contractor, Fiera Milano Stand Builder, Exhibition Fabrication Services Europe.)
+#CPHI2026 #CPHIMilan #ExhibitionDesign #BoothDesign #TradeShowBooth #ExhibitionStand #StallFabrication #EventMarketing #BrandExperience #HKCommunication #ExhibitionContractor #FieraMilano #PharmaExhibition #InternationalExhibition #ExhibitionExperts</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-06-22 10:08:01</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Dubai Stand Builder</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dubai-stand-builder-406322214?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAADYnFcYB0rlbkJnaLtw6U7xlrmad1ejacow</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/feed/update/urn:li:groupPost:1908847-7474724956203839489?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsABCwBsx4fHkp61BwbvkLPvpYju73n3x4</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Exhibition Booth Construction Services Available Across
+UAE &amp; Saudi Arabia. Partner with us for custom-designed exhibition stands, seamless execution, and on-site support. 
+Dubai Stand Builder 
+Design - Build - Install 
+Factory Located in Al Quoz Industrial Area
++91 8191 00 5850 
++971 56 386 4997</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-06-19 07:26:07</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Expo Worldwide Ltd</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/expo-worldwide/posts</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/expo-worldwide_expoworldwide-exhibitionbooth-tradeshow-activity-7473607022924427265-O8bu?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsABCwBsx4fHkp61BwbvkLPvpYju73n3x4</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>🚀 One Booth. Unlimited Business Opportunities.
+The question isn't how many people visit your booth.
+The real question is how many visitors become qualified leads.
+A successful exhibition booth is built on strategy not luck. From attracting the right audience to converting conversations into customers, every detail matters.
+At EXPO Worldwide, we design exhibition booths that help brands stand out, generate quality leads, and grow their business globally.
+🌍 Serving: UAE | Europe | USA | Asia
++91 9350116878 | +36 20 541 4370
+🌐 www.expoworldwides.com
+Let's build an exhibition booth that delivers real business results.
+| Exhibition Booth Design, Exhibition Stand Builder, Trade Show Booth, Exhibition Services, Custom Booth Design, Lead Generation |
+#ExpoWorldwide #ExhibitionBooth #TradeShow #LeadGeneration #ExhibitionMarketing #BoothDesign #B2BMarketing #EventMarketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-06-17 14:52:17</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>VCRAFT STUDIO</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vcraft-studio/posts</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/vcraft-studio_beautyworld-beautyworldmiddleeast-beautyworld2026-activity-7472994528438800384-xqrM?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsABCwBsx4fHkp61BwbvkLPvpYju73n3x4</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Make your brand shine at #Beautyworld Middle East 2026!
+📍 Dubai World Trade Centre, Dubai, UAE
+📅 06–08 October 2026
+At VCRAFT STUDIO, we design and build exhibition stands that help brands stand out, engage visitors, and generate business opportunities.
+✔ Custom Stand Design
+✔ Premium Booth Fabrication
+✔ End-to-End Project Management
+✔ On-Time Delivery
+Book your exhibition stand builder today and make a lasting impact at Beautyworld Middle East 2026.
+📞 EUROPE : +48732127137 | USA: +1 (332) 238-4624 | Netherland : +3197010283232
+📧 info@vcraftstudio.com
+#BeautyworldMiddleEast #Beautyworld2026 #DubaiEvents #CosmeticsIndustry #BeautyIndustry #ExhibitionStandBuilder #BoothDesign #TradeShowMarketing #VCraftStudio #ExhibitionDesign</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-06-11 16:41:31</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Expo Events Consulting</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/expoeventsconsulting/posts</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/expoeventsconsulting_planning-for-atm-2026-hire-expo-events-activity-7470847690659135489-tAuW?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsABCwBsx4fHkp61BwbvkLPvpYju73n3x4</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Planning for ATM 2026? 
+Hire Expo Events Consulting to build your premium custom stand at DWTC. We deliver turnkey booth design, fabrication, and installation for travel brands.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-06-17 08:35:38</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>HK Communication PVT.LTD.</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/hk-communication-pvt-ltd/posts</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/hk-communication-pvt-ltd_hkcommunication-appasamyassociates-apacra2026-activity-7472899741501038593-VCul?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsABCwBsx4fHkp61BwbvkLPvpYju73n3x4</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>✨ Proudly Unveiling the Appasamy Associates Stall at APACRA Pattaya 2026! 
+Designed and executed by Team HK Communication, this 21 SQM custom exhibition stall for Appasamy Associates showcases a perfect blend of creativity, innovation, and premium craftsmanship. Every detail has been thoughtfully curated to create a powerful brand presence, maximize visitor engagement, and deliver an exceptional exhibition experience on the international stage.
+🌏 Taking Indian exhibition excellence to Pattaya, Thailand with world-class booth design and fabrication.
+📍 Event: APACRA Pattaya 2026
+Location: Pattaya, Thailand
+🏢 Stall Size: 21 SQM
+A heartfelt thank you to Appasamy Associates for trusting HK Communication with this international exhibition project. We are proud to deliver innovative exhibition solutions that help brands stand out globally.
+📍 HK Communication Offices
+India Office:
+Plot No. 31A, Kakrola Gaon, Dwarka Sector 16B, Opp. Govt. School, New Delhi, Delhi – 110078
+UAE Office:
+2 Street 5, Al Quoz, Dubai, United Arab Emirates
+Exhibition Stall Design | Booth Fabrication | Custom Exhibition Booth | Trade Show Booth | Exhibition Contractor | Exhibition Stand Builder | International Exhibition | APACRA 2026 | Pattaya Thailand | Medical Exhibition | Exhibition Design Company | Booth Design | Exhibition Services | Event Branding | Brand Experience | Turnkey Solutions | HK Communication | Appasamy Associates | India to Thailand | Exhibition Fabrication
+#HKCommunication #AppasamyAssociates #APACRA2026 #PattayaThailand #ThailandExhibition #ExhibitionDesign #StallDesign #BoothDesign #TradeShow #ExhibitionBooth #BoothFabrication #CustomBooth #ExhibitionStand #InternationalExhibition #ExhibitionContractor #EventBranding #ExperientialMarketing #BrandActivation #MedicalExhibition #TurnkeySolutions #GlobalExhibitions #MadeByHK #Thailand #Pattaya #ExhibitionServices</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-06-22 09:26:34</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Dubai Stand Builder</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dubai-stand-builder-406322214?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAADYnFcYB0rlbkJnaLtw6U7xlrmad1ejacow</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/dubai-stand-builder-406322214_exhibition-booth-construction-services-available-activity-7474724499851071488-KOpP?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsABCwBsx4fHkp61BwbvkLPvpYju73n3x4</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Exhibition Booth Construction Services Available Across
+UAE &amp; Saudi Arabia. Partner with us for custom-designed exhibition stands, seamless execution, and on-site support. 
+Dubai Stand Builder 
+Design - Build - Install 
+Factory Located in Al Quoz Industrial Area
++91 8191 00 5850 
++971 56 386 4997</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-06-10 09:57:18</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>The Builder UAE</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/the-builder-uae/posts</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/the-builder-uae_creating-impactful-brand-experiences-through-activity-7470383581828313088-rfZx?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsABCwBsx4fHkp61BwbvkLPvpYju73n3x4</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Creating impactful brand experiences through innovative exhibition booths, digital signage solutions, smart displays, and reliable facility maintenance services.
+From concept and fabrication to installation and ongoing support, we deliver solutions that enhance visibility, engagement, and operational efficiency.
+✔ Exhibition Booths
+✔ Digital Signage Systems
+✔ LED &amp; Smart Displays
+✔ Facility Maintenance
+Let's bring your brand and spaces to life.
+📞 +971 2 6310110
+🌐 www.thebuilder-uae.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-06-11 12:00:04</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>VCRAFT STUDIO</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vcraft-studio/posts</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/vcraft-studio_dubaiderma2026-exhibitionstanddesign-boothbuilder-activity-7470776862743416832-RvUK?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsABCwBsx4fHkp61BwbvkLPvpYju73n3x4</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Exhibiting at Dubai Derma 2026?
+Make sure your booth works as hard as your team.
+From custom stand design to complete execution, VCRAFT STUDIO helps brands attract more visitors, generate quality leads, and create memorable experiences.
+📍 Dubai, UAE
+Book your exhibition stand builder today
+📞EUROPE : +48732127137 | USA: +1 (332) 238-4624 | Netherland : +3197010283232
+📧 info@vcraftstudio.com
+#DubaiDerma2026 #ExhibitionStandDesign #BoothBuilder #VCraftStudio #TradeShowSuccess</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-07-10 16:17:14</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Infinity Plus - Brand Solutions</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/infinityplusint/posts</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/infinityplusint_uae-retailbranding-shelfdisplay-activity-7481350831187857408-W0rl?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsABCwBsx4fHkp61BwbvkLPvpYju73n3x4</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>The Shelf Is a Battlefield ⚔️📦
+Win Attention Before Your Competitors Do.
+Every product is competing for the same glance. Eye-catching displays, premium packaging, and impactful branding give your product the advantage it needs to stand out, attract customers, and drive sales.
+#UAE #RetailBranding #ShelfDisplay #InfinityPlus #BrandVisibility #CreativeBranding #DubaiBranding #MarketingSolutions #VisualMerchandising #PackagingDesign #BusinessBranding
+Retail shelf branding Dubai | Shelf display solutions UAE | Product visibility Dubai | Visual merchandising UAE | Premium packaging Dubai | Retail branding solutions UAE | Creative branding agency Dubai | Product presentation UAE | Marketing design Dubai | Business branding UAE</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-07-08 07:44:34</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>孔晶晶(Zoey)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/%E6%99%B6%E6%99%B6-zoey-%E5%AD%94-88a474412?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAAGkTZuoBD32SAdMmNy8T4uVS4Hen01D-Hog</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/%E6%99%B6%E6%99%B6-zoey-%E5%AD%94-88a474412_retaildesign-designformanufacturing-retailfixtures-activity-7480497036908449792-7DOX?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsABCwBsx4fHkp61BwbvkLPvpYju73n3x4</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Before we cut a single sample, we ask design agencies 5 questions.
+Most factories skip all of them.
+Here's why that matters — and what each question actually solves:
+—
+Question 1: "What's the store environment like?"
+A fixture going into a Dubai mall with intense spotlights needs different finish treatment than one in a Scandinavian concept store with soft diffused lighting.
+Matte black powder coat looks stunning in renderings — but shows every fingerprint in a high-touch retail environment.
+If we don't ask, we choose wrong. And your client sees the problem on Day 1.
+—
+Question 2: "What's the actual product weight per shelf?"
+Designers spec shelf dimensions based on aesthetics. We check physics.
+An 800mm span acrylic shelf holding 6kg of perfume bottles? That flexes. Visibly.
+We calculate load and recommend material thickness or hidden reinforcement — before sampling. Not after complaints.
+—
+Question 3: "Has flat-pack been considered for shipping?"
+A fully assembled 1.8m display tower costs ~$220 to ship per unit by sea. The same unit engineered for flat-pack? ~$135.
+That's a 40% saving — often the difference between a project being approved or killed by procurement.
+We can redesign joints and connections to enable flat-pack without changing the look. But it has to be planned from Day 1.
+—
+Question 4: "Who assembles this in-store? Professional installers or store staff?"
+If store staff assemble it, the design must be foolproof. No special tools. No ambiguous steps.
+We engineer cam locks, magnetic connections, and numbered components so store staff can set it up in minutes, not hours.
+If we don't ask, the client calls the agency three weeks later saying nobody can figure out how to build it.
+—
+Question 5: "Is this a 1-store pilot or a 200-store rollout?"
+A pilot sample and a rollout-ready design are engineered differently.
+For rollout, we plan for production consistency, packaging efficiency, spare parts, and regional logistics.
+If we engineer for pilot only, and you suddenly need 200 units, the design may not scale.
+—
+These five questions take 15 minutes.
+They prevent problems that would otherwise take 15 weeks to fix.
+If your current factory just says "send the drawing, we'll make a sample" without asking anything — that's not a manufacturing partner. That's a risk you're absorbing without knowing it.
+If you're working on a project brief right now and want a second set of eyes on the engineering side, feel free to send it over. Happy to share thoughts.
+#RetailDesign #DesignForManufacturing #RetailFixtures #ManufacturingPartner</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-07-06 20:00:13</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Solo De Zin | Creative Studio</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/solodezin/posts</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/solodezin_solodezin-creativeagency-dubaibusiness-activity-7479957393595064321-w-Lr?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsABCwBsx4fHkp61BwbvkLPvpYju73n3x4</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>A new chapter for premium digital production in Dubai. 🇦🇪
+Welcome to the official company page for Solo De Zin | Creative Studio!
+To everyone joining from my personal network—thank you for the support. I launched this agency with a simple, uncompromising vision: to eliminate generic, template-driven branding and replace it with high-performance, commercially-driven visual architecture.
+We don't just create content; we build digital ecosystems engineered to perform. Our team is fully set up to deliver end-to-end premium execution across 8 core pillars:
+Commercial Photography &amp; Video Production (Product, Food &amp; Industrial)
+Bespoke Web Design &amp; Architecture
+Technical SEO &amp; Advanced GEO (AI Search Engine Optimization)
+Social Media Management &amp; Strategy
+Visual Identity, Graphic Design &amp; Packaging Design
+Whether you are looking to scale your brand’s visual identity or maximize your conversion rate online, we are built to take your digital presence to the next level.
+👉 Follow our page to see our latest project case studies, behind-the-scenes production workflows, and digital marketing insights.
+Let’s build something incredible.
+Marwan Amra Founder &amp; Creative Director, Solo De Zin 📩 info@solodezin.com | 🌐 www.solodezin.com
+#SoloDeZin #CreativeAgency #DubaiBusiness #WebDesign #CommercialPhotography #MarketingStrategy #DubaiStudio</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:00:35</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Contemporary Connect</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/contemporary-connect/posts</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/contemporary-connect_brandbuilding-contentcreation-creativedirection-activity-7475880623576915969-6mW_?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsABCwBsx4fHkp61BwbvkLPvpYju73n3x4</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Building a brand requires more than a single touchpoint.
+A true 360° approach brings together branding, content, creative direction, packaging, photography, and visual storytelling to create a consistent brand experience.
+Every detail plays a role in how a brand is perceived—from the first impression to the lasting memory it leaves behind.
+Established in 2014, we've helped businesses across the UAE and India create experiences that connect, engage, and stand out.
+📩 Looking for a complete brand-building partner? Let's connect.
+[360 branding agency UAE, content creation Dubai, creative direction UAE, brand photography Dubai, packaging design UAE]
+#BrandBuilding #ContentCreation #CreativeDirection #BrandStrategy #ContemporaryConnect
+بناء علامة تجارية قوية يتطلب أكثر من نقطة تواصل واحدة.
+يعتمد النهج المتكامل 360° على الجمع بين بناء الهوية، وصناعة المحتوى، والتوجيه الإبداعي، والتغليف، والتصوير، وسرد القصص البصرية لخلق تجربة متكاملة للعلامة التجارية.
+كل تفصيل يساهم في تشكيل الصورة الذهنية للعلامة التجارية، من الانطباع الأول وحتى الأثر الذي يبقى في الذاكرة.
+منذ عام 2014، ساعدنا الشركات في الإمارات والهند على بناء تجارب تواصل مؤثرة وتترك انطباعاً مميزاً.
+📩 هل تبحث عن شريك لبناء علامتك التجارية بشكل متكامل؟ تواصل معنا.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-06-25 12:59:53</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ABN18 STUDIOS - BRANDING &amp; ADVERTISING AGENCY</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/abn18-studios-branding-advertising-agency/posts</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/abn18-studios-branding-advertising-agency_hawaii-snacks-print-activity-7475865345703194626-RELl?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsABCwBsx4fHkp61BwbvkLPvpYju73n3x4</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>COCONUT  FLAVOURED CANDY STANDY POUCH PACKAGING DESIGN FOR SILKLAND CONFECTIONARY.
+For Design Enquiry, please reach out to us Call/Whatsapp on +91 9687228811 / +91 9687 182288 or at infuse@abn18studio.com
+تصميم عبوة قائمة (Stand-up pouch) لحلوى بنكهة جوز الهند، مخصصة لمنتجات "سيلك" (Silk) والحلويات
+#hawaii #snacks #print #packaging #fmcg #packaging #packagingdesign #branding #branddesign #namkeen #confectionary #cakeoftheday #chocolatebar #wrapper
+#unitedstates #california #newyork #texas #newjersey #scotland #wales 
+#arizona #hawaii #nevada #sanjose #losangeles #sanfrancisco #lasvegas #england #netherland #france #spain #italy #greece #denmark #amsterdam #russia #dubai #qatar #saudiarabia #turkey #istanbul #impex #export #import #distributor #printing #business #foodbusiness #everything
+#abudhabi #australia #belgium #pakistan #nepal #iran #iraq #philippines #singapore #malaysia #indonesia #middleeast #apac #emea
+#mea #newzealand #america #canada #uk #ireland #germany #spain 
+#southafrica#manufacturing #masala #spices #chickenmasala #hot #spicy #manufacturer #usa #wrapper</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-07-08 18:58:42</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Infinity Plus - Brand Solutions</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/infinityplusint/posts</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/infinityplusint_uae-packagingdesign-brandstory-activity-7480666689542578176-edxQ?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsABCwBsx4fHkp61BwbvkLPvpYju73n3x4</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Your Packaging Should Tell a Story 📦✨
+Every package is an opportunity to communicate your brand. Thoughtful design, premium materials, and refined finishes turn ordinary packaging into an experience that captures attention, builds trust, and leaves a lasting impression.
+#UAE #PackagingDesign #BrandStory #InfinityPlus #CreativeBranding #DubaiBranding #MarketingSolutions #PremiumPackaging #BrandExperience #ProductBranding #BusinessBranding
+Packaging design Dubai | Custom packaging UAE | Brand storytelling through packaging Dubai | Premium packaging solutions UAE | Product packaging design Dubai | Creative branding agency UAE | Luxury packaging Dubai | Packaging and printing UAE | Brand presentation Dubai | Business branding UAE</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-06-24 09:57:26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Niraj Vedwa</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nirajvedwa?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAAAEh4xUBN_a8g7dNRrj0h-GYA7fFf_IqSdo</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/nirajvedwa_leadership-digitaltransformation-artificialintelligence-activity-7475457045274562560-96zW?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsABCwBsx4fHkp61BwbvkLPvpYju73n3x4</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Great meeting my childhood family friend and schoolmate, Rahul Nagpal, Chairman GP Inc. in  Dubai today. He has built GP Inc to a leadership position in the Middle East. The group today offers an end-to-end proposition across Digital Marketing, PR, Media, Brand Advisory &amp; Strategy, E-Commerce, and Advertising—a truly unique and integrated model that is rarely seen in the industry.
+It was fascinating to discuss how Data, Analytics, and AI can be leveraged to deliver measurable, outcome-based value for customers.
+Combining my experience in Data, Analytics, Agentic AI, and Generative AI with Rahul’s deep expertise in marketing analytics and data monetisation, I believe there is tremendous potential to create meaningful impact for businesses.
+The companies in his ecosystem portfolio include:
+• Tuesday – A creative powerhouse focused on brand transformation, advertising, and storytelling to build lasting brand impact.
+ +• Thirty 31 North – Delivers market research and strategic brand intelligence to enable informed business decisions.
+ +• The Behavior Lab – Uses data-driven insights to craft impactful marketing strategies and deepen consumer engagement.
+ +• Tonnit &amp; Co – A dynamic agency specialising in branding, design, packaging, and content development.
+ +• Tickle24 – Creates compelling podcasts and engagement platforms that strengthen brand positioning.
+ +• Mobiiworld – Develops cutting-edge mobile applications and digital platforms that enhance customer experiences and accelerate business growth.
+Exciting possibilities lie ahead at the intersection of marketing, data, and AI.
+#Leadership #DigitalTransformation #ArtificialIntelligence #GenerativeAI #AgenticAI #DataAnalytics #DataMonetisation #DigitalMarketing #BrandStrategy #CustomerExperience #Innovation #MiddleEast #Partnerships #BusinessTransformation</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-06-23 01:29:18</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>JAM Branding &amp; Design Agency</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wearejambranding/posts</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/wearejambranding_packagingdesign-brandstrategy-influencermarketing-activity-7474966781644800000-GtrP?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsABCwBsx4fHkp61BwbvkLPvpYju73n3x4</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Launching a new product is one thing.
+Creating a system that keeps consumers coming back is another.
+For SweetUnion, Allied Pinnacle needed more than packaging. They needed a brand platform capable of supporting a continual pipeline of limited-edition flavour drops while remaining instantly recognisable on shelf.
+JAM developed the packaging system across launches including Dubai Pistachio Chocolate and Yuzu Lemon, creating a flexible framework that allows new flavours to launch every 12 weeks without losing brand recognition.
+But the launch didn't stop at the shelf.
+To drive discovery and retail conversion, we developed and managed a creator-led influencer strategy designed to connect social buzz with in-store action.
+From creator sourcing and briefing through to content management and rollout, every touchpoint was built to generate excitement, urgency and trial.
+The result is a repeatable launch platform where packaging, social content and retail work together to turn each flavour drop into a brand moment.
+Because in today's market, great packaging gets attention. Great launch strategy gets people to store.
+.
+.
+.
+.
+.
+#PackagingDesign #BrandStrategy #InfluencerMarketing #RetailMarketing #FMCGMarketing #PackagingDesignAgency #CreativeAgency #JAMAgency</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-06-22 10:57:58</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Priyanka Ashar</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/priyanka-ashar?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAAArqvGgBk_LX23jGl61JU8Bvrr84nLAIRbI</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/priyanka-ashar_hello-uae-network-im-in-dubai-until-25th-activity-7474747503611920384-cg9E?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsABCwBsx4fHkp61BwbvkLPvpYju73n3x4</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Hello UAE Network,
+I’m in Dubai until 25th June and would love to connect with founders, business owners, and fellow professionals who want to strengthen their digital presence. 
+I’m the Co-Founder of Little Tricks Media, a 360° Digital Marketing agency founded in 2018. Over the years, we’ve had the opportunity to work with brands across the UAE, USA, Canada, UK, Hong Kong, Belgium, and India, helping them build meaningful brand identities and stronger digital experiences.
+Our expertise spans:
+• Social Media Marketing
+• Branding &amp; Packaging
+• Website Design &amp; Development
+• Performance Marketing
+We’ve worked with brands across industries including F&amp;B, real estate, fashion, home décor, jewellery, education, and more.
+If you’re a founder, part of a growing team, or know someone I should connect with while I’m here, I’d love an introduction.
+Feel free to DM me or leave a comment below.
+Looking forward to some meaningful conversations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-06-21 12:00:03</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Zenzele Mntambo</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/zenzele-mntambo?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAAEIhBN8B9XgVCgU8LQh6c3gJxVgFntosEQ0</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/activity-7474400738287181824-Bgo_?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsABCwBsx4fHkp61BwbvkLPvpYju73n3x4</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>KFC just rolled out one of the biggest rebrands in its history.
+JKR (the agency behind Burger King's glow-up) led it. Here's what actually changed:
+The bucket became the system. Not a logo tweak, they rebuilt the bucket itself into something that can hold photography, illustration, and campaign messaging. 
+It's no longer packaging. It's a frame for everything KFC says.
+The Colonel got upgraded, not replaced. Thicker outline, a neck and collar, a warmer expression. Still unmistakably him, just more dimensional. The brand name now sits beside him instead of underneath.
+Two new custom typefaces. Kentucky Fried Serif and Kentucky Fried Sans, built with StudioD RAMA. The lettermark is simpler and more legible than before.
+"Finger Lickin' Good" stopped being a tagline. It's now a behavioral standard, applied to ordering, hospitality, restaurant design, and app experience. Not something they say. Something every touchpoint has to prove.
+They're building a beverage platform, Kwench by KFC. And experimenting with QXR: quick experience restaurants. New flagship locations are landing later this year in Texas and Dubai, fully immersive, built around the new identity.
+JKR calls the whole thing the Bucketverse.
+Here's what stands out to me:
+KFC didn't start over. They took the one asset that already had 70 years of recognition baked in, the bucket, and instead of replacing it, they made it work harder. That's the move. Not "let's look different." It's "let's make the thing people already trust do more."
+Rolling out now in the UK and Ireland, then Australia and the US through 2026, eventually reaching 34,000+ restaurants in 150+ countries. Worth watching how this plays out.
+#KFC #Bucketverse #Rebranding #BrandStrategy #JKR #BrandIdentity #MarketingStrategy #CreativeDirection #DesignThinking #QSR #BrandDesign #MarketingNews</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-07-07 18:38:29</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Infinity Plus - Brand Solutions</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/infinityplusint/posts</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/infinityplusint_uae-visualbranding-packagingdesign-activity-7480299212140769280-KDH2?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsABCwBsx4fHkp61BwbvkLPvpYju73n3x4</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>People Buy with Their Eyes First 👀✨
+Design Accordingly.
+Before customers read about your product, they see it. Strong design, premium packaging, and professional branding create the confidence that turns attention into action. Make every visual detail work in your favor.
+#UAE #VisualBranding #PackagingDesign #InfinityPlus #CreativeBranding #DubaiBranding #MarketingSolutions #BrandPerception #ProductBranding #DesignMatters #BusinessBranding
+People buy with their eyes first Dubai | Visual branding UAE | Premium packaging Dubai | Product presentation UAE | Creative branding agency Dubai | Brand perception solutions UAE | Professional branding Dubai | Marketing design UAE | Business branding solutions Dubai | Packaging and print UAE</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-06-17 17:37:56</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Creative Rehman</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/crea8iverehman?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAAAOSDMYBrf3uF6hbRVBb4_vc_gFCu4czm4M</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/crea8iverehman_graphicdesign-branding-logodesign-activity-7473036219367542784-dZGS?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsABCwBsx4fHkp61BwbvkLPvpYju73n3x4</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>🚀 Great Design Doesn't Just Look Good. It Drives Business Growth.
+In today's competitive market, your brand has less than 3 seconds to make a first impression.
+Is your business standing out or blending in?
+I help companies transform their ideas into powerful visual identities that build trust, attract customers, and increase conversions.
+🎨 Graphic Design Services:
+✅ Logo Design &amp; Brand Identity
+✅ Social Media Creatives
+✅ Company Profiles &amp; Brochures
+✅ Business Cards &amp; Stationery
+✅ Website &amp; Landing Page Graphics
+✅ Real Estate Marketing Designs
+✅ Product Packaging
+✅ Infographics &amp; Presentations
+✅ Digital Advertising Creatives
+✅ AI-Powered Marketing Visuals
+💡 Why Clients Choose Me:
+✔ 10+ Years Professional Experience
+✔ Modern, Clean &amp; Conversion-Focused Designs
+✔ Fast Turnaround Time
+✔ Unlimited Creative Solutions
+✔ Reliable Communication
+✔ Results-Driven Approach
+Whether you're a startup in the USA, a growing business in Dubai, a real estate agency, or an eCommerce brand, I can help elevate your visual presence and strengthen your brand.
+📩 Looking for a professional designer who understands business goals, not just design?
+Let's connect and discuss your next project.
+#GraphicDesign #Branding #LogoDesign #BusinessGrowth #Marketing #DigitalMarketing #Entrepreneur #Startup #SmallBusiness #RealEstateMarketing #Ecommerce #WebDesign #SocialMediaMarketing #CreativeDesign #BusinessOwner #USAStartups #DubaiBusiness #UAEBusiness #BrandIdentity #MarketingStrategy #LinkedInMarketing #ContentMarketing #DigitalAgency #Freelancer #DesignServices #BusinessDevelopment #LeadGeneration #CreativeAgency #ProfessionalDesigner #GrowthMarketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-06-17 13:25:21</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Shiza Munir</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shiza-munir-graphicdesigner?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAAEYuwBoBOkuRljrIzar1wkGbD5OJ3Af1nqc</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/shiza-munir-graphicdesigner_graphicdesign-branddesigner-freelancing-activity-7472972653784461312-Ggwc?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsABCwBsx4fHkp61BwbvkLPvpYju73n3x4</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>A Dubai agency hired me.
+No video call.
+No face reveal.
+And We worked remotely together for over 2 years.
+At the time, I thought my niqab might be a disadvantage in a visual industry.
+I was wrong.
+They didn't hire me because of how I looked.
+They hired me because of the work I delivered.
+What started as a simple test task turned into:
+✅ 100+ design projects
+✅ 50+ brand accounts
+✅ Meta Ads creatives
+✅ Packaging designs
+✅ Amazon listing visuals
+And during those 2 years, one thing became very clear:
+Clients care far more about reliability than visibility.
+Here's what actually got me hired and kept me there:
+→ Clear communication from day one
+→ A portfolio focused on results, not just aesthetics
+→ Consistent updates without being asked
+→ Delivering on time. Every single time.
+The lesson?
+Many talented people hold themselves back because they think they don't fit the "ideal image."
+But most clients aren't looking for perfection.
+They're looking for someone they can trust.
+Your work speaks louder than your appearance ever will.
+✨ I'm sharing lessons from design, branding, freelancing, and professional growth. Follow along if that interests you.
+Have you ever held yourself back for a reason that had nothing to do with your actual skills?
+#GraphicDesign #BrandDesigner #Freelancing</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-06-17 09:21:24</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Erik Hedlund</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/erikhedlund?miniProfileUrn=urn%3Ali%3Afsd_profile%3AACoAAAA-pngB5j6B0PRD7p9GpQA4Gkov0rDcTj8</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/erikhedlund_when-revenue-flatlines-and-the-board-panics-activity-7472911261576601600-iSpj?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsABCwBsx4fHkp61BwbvkLPvpYju73n3x4</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>When revenue flatlines and the board panics, a CEO inevitably stares out the window and whispers the most dangerous words in strategy:
+"We need a rebrand. We need to look younger."
+This week, KFC launched a massive global brand revamp. When a 90-year-old legacy corporation does this, it usually signals disaster. What typically follows is the corporate equivalent of treating a heart attack with an expensive facelift. Remember the recent Cracker Barrel fiasco that sparked outrage all the way to the White House?
+Treated as a siloed marketing exercise, the "rebrand" becomes a mythical silver bullet meant to magically cure fundamental business rot.
+The root cause? Most CEOs have absolutely no clue how brand building works. As Mark Ritson points out, even most marketers don’t know the fundamentals. The Board and Management gets bored of their own logo, so they pay an agency millions to torch decades of accumulated equity and replace it with a bland, minimalist sans-serif font.
+They ignore behavioral science. Customers do not get bored of your brand. They just want you to be distinct and instantly recognizable.
+Destroying Distinctive Brand Assets (DBAs) for "modern relevance" rarely attracts new demographics, it just alienates the ones who pay the bills. It is exactly what Andrew Tindall at System1 warns about: sacrificing the immense financial power of "compound creativity" for a cheap, short-term thrill. Most rebrands are just million-dollar lipstick applied to a broken business model.
+So, when KFC unveiled their new identity, the stage was set for another vanity project.
+But they didn't torch the house. They delivered a masterclass in modernizing without losing your commercial soul.
+First, they ruthlessly protected their DBAs. They didn't hide the Colonel. Instead, they anchored the entire refresh around their most iconic asset: the bucket. By introducing the "Bucketverse," they built an entertaining creative arena directly connected to the physical product. It is a textbook execution of the physical and mental availability Byron Sharp preaches.
+More importantly, this isn't just an agency playing with pantones. It is the packaging for a massive business and operational pivot.
+KFC is using this rebrand to restructure its entire menu and distribution model. They are expanding into boneless chicken, launching a global sauce "pantry," introducing the "KWENCH" beverage platform to drive foot traffic beyond mealtimes, and rolling out next-gen restaurants from Texas to Dubai.
+The new brand identity is merely the signal. The underlying business and product strategy is the actual engine.
+You cannot design your way out of a broken business model. A rebrand should be a multiplier of a competitive strategy, never a substitute for one.
+How many billions are currently being incinerated in boardrooms across the world, desperately trying to fix a flawed strategy with a new font?</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-06-16 14:40:01</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Hospitality Career Profile</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/hospitalitycareerprofile/posts</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/hospitalitycareerprofile_kfc-rebrand-brandidentity-activity-7472629054307950592-qUAc?utm_source=social_share_send&amp;utm_medium=member_desktop_web&amp;rcm=ACoAAGsABCwBsx4fHkp61BwbvkLPvpYju73n3x4</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>KFC is getting a makeover. 🍗 The chain has refreshed its iconic bucket and Colonel Sanders logo (via agency JKR) and is rolling out a "modern chicken" strategy expanded boneless items, a global sauce platform, a new KWENCH by KFC drinks line, and next-gen restaurant designs in Texas and Dubai.
+Read more 👉 https://lnkd.in/dW6KEG2M
+#KFC #Rebrand #BrandIdentity #ModernChicken #KWENCH #JKR #QSR #FastFood #RestaurantDesign #Packaging #Branding #FoodNews #ColonelSanders #FriedChicken</t>
         </is>
       </c>
     </row>
